--- a/LatAm_Power_Companies_Research.xlsx
+++ b/LatAm_Power_Companies_Research.xlsx
@@ -13,6 +13,8 @@
     <sheet name="PPAs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Notes &amp; Verification" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Key Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gas &amp; Investment Hurdle Rates" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Hurdle Rates - Coverage &amp; Gaps" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +79,14 @@
       <color rgb="007F7F7F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +103,33 @@
         <fgColor rgb="00EAF0F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -118,11 +151,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -176,6 +253,65 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9296,4 +9432,1982 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="58" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Stated hurdle rates / target returns relevant to gas, PPAs &amp; investment — 18 listed LatAm power companies (official sources first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Key finding: NO company in this list publishes a clean gas-fired-generation IRR hurdle the way NRG/Vistra/RWE/AGL do. Closest data points below. NOTE: the two most gas-relevant names (Eneva, Colbún) could not be fully checked — this environment's network egress policy blocks their official domains (api.mziq.com, colbun.cl). See the 'Coverage &amp; Gaps' tab. Every quote here was captured via web-search of official sources; direct fetches of many official PDFs were 403-blocked, so page-level verbatim was often unavailable (noted per row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Stated rate</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Gas-
+specific?</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Date of statement</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Source type</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Official?</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Verbatim quote</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Source detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>A · Gas-specific</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Grupo Energía Bogotá</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>GEB CB</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>gas transport</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>regulated (RAB) WACC for gas transport</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>11.88% (raised from 10.94%); rate rolled back / refund ordered by CREG in 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>pre-tax (antes de impuestos), real (pesos constantes / constant COP)</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Resolución CREG 102 002 de 2023 (approved CREG session 1271, 2 June 2023). Base rate/methodology: Resolución CREG 103 de 2021 (10.94% en pesos constantes antes de impuestos). CORRECTION: draft cited 'CREG 004/175 de 2021' as the base — the 10.94% base rate is actually from Resolución CREG 103 de 2021 (Res. 175 de 2021 is a separate general remuneration methodology).</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>regulatory filing</t>
+        </is>
+      </c>
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>"...un incremento en la tasa de descuento del costo de capital (WACC), que pasó de 10,94% a 11,88% en 2023 mediante la Resolución CREG 102 002, permitiendo a empresas transportadoras como TGI —filial del Grupo de Energía de Bogotá— incrementar costos en la componente de transporte." / "CREG Resolution 103 of 2021 with a WACC of 10.94% in constant pesos before taxes" ("...an increase in the discount rate / cost of capital (WACC), which went from 10.94% to 11.88% in 2023 via CREG Resolution 102 002, allowing transport companies such as TGI —subsidiary of Grupo de Energía de Bogotá— to increase costs in the transport component"; base rate of 10.94% set by CREG Resolution 103 of 2021, expressed in constant pesos before taxes). Source: Ministerio de Minas y Energía / El Nuevo Siglo / Infobae reporting on the CREG resolutions; primary CREG resolution text not directly retrievable (HTTP 403).</t>
+        </is>
+      </c>
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-ordena-devolver-mas-de-150-mil-millones-a-usuarios-de-gas-natural-por-cobros-adicionales-en-transporte/</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Regulator-set (CREG) WACC applied to gas transport activity, applicable to TGI (GEB's Colombian gas-transport subsidiary) and Promigas. Resolución CREG 102 002 de 2023 raised the tasa de descuento from 10.94% to 11.88% (increase justified by the 35% income-tax rate under Ley 2277 de 2022). Figure corroborated across multiple official/press sources: Ministerio de Minas y Energía, Forbes Colombia, Infobae, El Colombiano, Semana, El Nuevo Siglo. Primary CREG pages (gestornormativo.creg.gov.co originals + htm, suin-juriscol.gov.co) all returned HTTP 403 to automated fetch, so no verbatim pull from the primary CREG document was possible. IMPORTANT: this is a regulator-set RAB return, NOT an investment hurdle rate independently declared by GEB. In March 2026 CREG upheld appeals, ordered the WACC reduced and ~COP 150bn overcharged (2023-present) refunded to users, so the 11.88% rate is rolled back / under dispute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>A · Gas-specific (regulatory / historical)</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>AES Brasil / AES Corp</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>AESO3 BZ</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>named gas project</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>regulated / regulatory return (ANEEL WACC embedded in the plant's tariff/CVU)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>7.16% (described as a real return, already net of taxes)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>Real, post-tax ('real index foreseen for generators, based on WACC, already discounting taxes'), BRL. This is a regulator-set (ANEEL) WACC used in the Uruguaiana gas-fired thermal plant's variable-cost/tariff (CVU) calculation, NOT a hurdle rate stated by AES. In the underlying 2015 dispute the generator had applied a 10% rate and ANEEL imposed 7.16%, so 7.16% is ANEEL's figure, expressly not AES's own return expectation. Levered/unlevered: not stated (regulatory WACC).</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>ANEEL determination for the AES Uruguaiana gas-fired thermal plant; the 7.16% vs 10% dispute references February 2015. Plant divested by AES in 2020. Exact determination date not confirmed from an official AES source.</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>news (reporting an ANEEL regulatory determination) — third party</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>Per the source summary (Portuguese, translated): the 7.16% 'is the real index foreseen for generators, based on the calculation of WACC (weighted average cost of capital), already discounting taxes; the CVU was calculated based on a regulatory return rate of 7.16% per year' — versus the 10% rate the generator had applied. Full primary-page verbatim not accessible (page 403-blocked); wording confirmed via WebSearch summary.</t>
+        </is>
+      </c>
+      <c r="N5" s="23" t="inlineStr">
+        <is>
+          <t>https://www.canalenergia.com.br/noticias/4931313/aneel-mantem-taxa-de-retorno-de-uruguaiana-em-716</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>CanalEnergia article 'Aneel mantem taxa de retorno de Uruguaiana em 7,16%'. Reports ANEEL keeping the regulatory return for the Uruguaiana gas thermal plant at 7.16% (real, WACC-based, net of taxes) in the CVU calculation, over the generator's applied 10% rate. The CanalEnergia page returned a 403 proxy denial on direct WebFetch; wording confirmed via WebSearch result summary. Third-party source; regulator-set figure, not AES's own investment hurdle; AES/AES Brasil divested Uruguaiana in 2020.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Enel Generación Chile</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>ENELGXCH CI</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>renewables (standalone battery storage / BESS)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>spread over WACC</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>at least +300 bps above WACC (&gt;=300 basis points spread)</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>not stated (spread over the company's WACC; pre/post-tax and real/nominal not specified; currency not specified). This is storage/BESS-specific, explicitly NOT gas.</t>
+        </is>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>Enel Chile Q1 2026 earnings call, late April 2026 (call/results reported ~29 Apr - 4 May 2026)</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
+        <is>
+          <t>earnings call transcript</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>As reported consistently across transcripts of the official call: management stated the company advances standalone BESS projects only when returns are "at least 300 basis points above our WACC," and stress-tests them against more critical/stressed market scenarios. (Related: standalone BESS can be profitable, with higher profitability when the BESS is used to hybridize an existing power plant.) Exact primary-webcast wording could not be independently read due to proxy egress blocking (403).</t>
+        </is>
+      </c>
+      <c r="N6" s="27" t="inlineStr">
+        <is>
+          <t>https://www.insidermonkey.com/blog/enel-chile-s-a-nyseenic-q1-2026-earnings-call-transcript-1753951/</t>
+        </is>
+      </c>
+      <c r="O6" s="25" t="inlineStr">
+        <is>
+          <t>Enel Chile S.A. (NYSE:ENIC; intermediate parent of the listed entity Enel Generacion Chile) Q1 2026 earnings call, management remarks on standalone battery storage (BESS) capital allocation. Stated at the Enel Chile parent level, not at the listed entity Enel Generacion Chile. Verbatim wording corroborated identically across multiple independent transcript aggregators (Insider Monkey, Investing.com, Yahoo Finance highlights, AlphaSpread, Benzinga). The originally cited Seeking Alpha URL (article/4897916) could not be located in searches and is replaced here with a corroborated transcript page. All transcript pages and the official Enel Chile webcast return 403 at the agent proxy gateway (CONNECT policy denial), so the primary webcast/official transcript was not directly read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Enel Generación Chile</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>ENELGXCH CI</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>renewables (group Renewables business under Enel SpA plan)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>spread over WACC</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>~300 bps average IRR-WACC spread targeted for new (renewables) projects</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>not stated (average spread of project IRR over WACC; pre/post-tax and real/nominal not specified; group reports in EUR). Applies to the group Renewables business, not gas/thermal.</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>Capital Markets Day, 19-22 Nov 2024 (2025-2027 Strategic Plan)</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
+        <is>
+          <t>investor presentation</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t>As reported from Enel's official 2025-2027 Strategic Plan materials: the group Renewables business targets an approximately "300 bps average spread between IRR and WACC" for new projects (Enel Americas states the same ~300 bps average IRR-WACC spread for new generation projects). Exact slide text could not be independently read due to proxy egress blocking the enel.com PDF (403).</t>
+        </is>
+      </c>
+      <c r="N7" s="27" t="inlineStr">
+        <is>
+          <t>https://www.enel.com/content/dam/enel-com/documenti/investitori/informazioni-finanziarie/2024/2025-2027-strategic-plan.pdf</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t>Enel SpA (ultimate controlling group) 2025-2027 Strategic Plan / Capital Markets Day presentation. CORRECTION vs draft: the ~300 bps average IRR-WACC spread is specifically the target for the group RENEWABLES business (mirrored in Enel Americas' 2025-2027 generation plan), NOT a blanket group-wide-across-all-businesses metric as the draft implied by labeling it 'group-level'. Stated at Enel SpA group level for the renewables/generation business, not at Enel Chile or Enel Generacion Chile. The official enel.com PDF and enelamericas.com annexes return 403 at the proxy gateway; the figure and its renewables attribution are corroborated across multiple independent summaries of the official plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Engie Brasil / ENGIE</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>EGIE3 BZ</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>group-level</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>spread over WACC (IRR minus WACC)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>IRR minus WACC spread of at least 150-250 bps (reference ~200 bps), accompanied by an NPV/Capex value-creation criterion of ~20-25%</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>Not stated precisely. ENGIE group applies technology- and contract-differentiated WACCs; the portfolio is designed to deliver group WACC + ~200 bps. Pre/post-tax, real vs nominal and currency not specified by the company. NOTE: this is a controlling-parent (ENGIE SA, Paris-listed) group framework, NOT a figure stated by the Brazilian listed entity Engie Brasil Energia (EGIE3).</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>Reiterated at ENGIE group H1 2025 results (1 August 2025); framework set out earlier at ENGIE Capital Markets Day / investor updates (2023-2025)</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>earnings call transcript / investor presentation (group-level, controlling parent ENGIE SA)</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>Corroborated across multiple WebSearch results of official ENGIE documents (primary PDF could not be opened in this environment due to an egress-policy 403): ENGIE requires investments to match or exceed an IRR minus WACC spread of at least 150 to 250 basis points (reference ~200 bps), together with an NPV/Capex ratio of roughly 20-25%. [English; corroborated by search snippets of the ENGIE H1 2025 transcript and fact sheets, but not a page-level verified verbatim quote]</t>
+        </is>
+      </c>
+      <c r="N8" s="27" t="inlineStr">
+        <is>
+          <t>https://www.engie.com/sites/default/files/assets/documents/2025-08/ENGIE%20H1%202025%20-%20Transcript.pdf</t>
+        </is>
+      </c>
+      <c r="O8" s="25" t="inlineStr">
+        <is>
+          <t>ENGIE SA (Paris-listed controlling parent) H1 2025 results transcript, capital-allocation/investment-discipline section. Canonical IR path (dated 2025-08) verified as a live official URL via WebSearch; an equivalent mirror exists at https://www.engie.com/app/uploads/2026/03/ENGIE-H1-2025-Transcript.pdf (the URL cited in the original draft). The 150-250 bps IRR-WACC spread plus ~20-25% NPV/Capex criterion is corroborated by multiple official ENGIE documents (H1 2025 transcript and fact sheets). GROUP LEVEL, not the Brazilian listed entity. Page-level verbatim could not be extracted (see verification_notes: WebFetch blocked by egress policy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Celsia</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>CELSIA CB</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>company-wide</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>ROIC/ROCE target expressed as a spread over WACC</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>&gt;200 bps above WACC (target ROCE = WACC + &gt;200 bps)</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>not stated (pre/post-tax and real/nominal not specified; ROCE/WACC in COP implied)</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>Investor-relations page current as of 2025-2026 (objective reiterated in 2024 results and 2025 shareholder-assembly / EnergizarC communications)</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="inlineStr">
+        <is>
+          <t>Celsia tiene como meta, en la búsqueda constante de maximizar el ROCE (retorno sobre el capital invertido), estar por encima de 200 puntos básicos del WACC (costo promedio ponderado del capital). / EN: Celsia's goal, in its constant pursuit of maximizing ROCE (return on invested capital), is to be more than 200 basis points above the WACC (weighted average cost of capital).</t>
+        </is>
+      </c>
+      <c r="N9" s="27" t="inlineStr">
+        <is>
+          <t>https://www.celsia.com/es/inversionistas/celsia/por-que-invertir-en-celsia/</t>
+        </is>
+      </c>
+      <c r="O9" s="25" t="inlineStr">
+        <is>
+          <t>Celsia investor-relations page '¿Por qué invertir en Celsia?'. Verbatim quote confirmed via WebSearch snippet of this exact official URL; direct WebFetch/curl blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com), so page/section could not be cited from the rendered document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Celsia</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>CELSIA CB</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Energy Services segment ('Servicios de energía') — not company-wide</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>ROIC minus WACC spread target (segment)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>&gt; 118 bps ROIC-WACC spread (target for the Energy Services / 'Servicios de energía' business)</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>2024 results / 2025 shareholder assembly (EnergizarC value-creation program)</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>press release</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>Buscan la expansión del spread entre ROIC vs. WACC para que sea mayor a 118 puntos básicos en el negocio de Servicios de energía. / EN: They seek to expand the ROIC vs. WACC spread to be greater than 118 basis points in the Energy Services business.</t>
+        </is>
+      </c>
+      <c r="N10" s="27" t="inlineStr">
+        <is>
+          <t>https://www.celsia.com/es/noticias/en-la-asamblea-celsia-profundizo-sobre-su-valor-fundamental-y-resalto-que-el-retorno-total-al-accionista-tsr-en-el-2024-fue-del-362/</t>
+        </is>
+      </c>
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t>Celsia press release on the 2024 shareholder assembly / EnergizarC program; segment-level target for the 'Servicios de energía' (Energy Services) business. Confirmed via WebSearch snippet of this exact official URL; direct WebFetch blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>AES Brasil / AES Corp</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>AESO3 BZ</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>group-level</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>target return range (unlevered contracted return / ROIC-type, i.e. project IRR)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>12% to 15% (data-center PPAs at the 'higher end' of the range; management framed development toward the upper half)</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>Unlevered / contracted-return basis (multiple independent transcript summaries describe this as AES's '12%-15% unlevered returns guidance range' for renewable/PPA investments; analyst framed the question as 'contracted ROIC or unlevered returns'). Currency USD (parent group, AES Corporation). Real vs nominal: not stated. Pre-tax vs post-tax: not stated.</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>AES Corporation Q3 2025 earnings call, 5 November 2025</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>earnings call transcript</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>Corroborated across independent transcript summaries: on returns for recent data-center PPAs, 'The returns on these tend to be at the higher end of our 12% to 15% [range].' Characterized elsewhere as AES's '12%-15% unlevered returns guidance range' for renewable-energy investments/PPAs. English original. (Exact verbatim sentence not read from a primary page — all transcript hosts 403-blocked; wording reconstructed from multiple concordant search summaries.)</t>
+        </is>
+      </c>
+      <c r="N11" s="27" t="inlineStr">
+        <is>
+          <t>https://www.insidermonkey.com/blog/the-aes-corporation-nyseaes-q3-2025-earnings-call-transcript-1641160/</t>
+        </is>
+      </c>
+      <c r="O11" s="25" t="inlineStr">
+        <is>
+          <t>AES Corporation (parent) Q3 2025 earnings call, 5 Nov 2025 — Q&amp;A. Analyst Dimple Gosai (Bank of America) asked how the contracted ROIC / unlevered returns on recent data-center PPAs compared to the legacy book; CEO Andres Gluski answered that returns tend to be at the higher end of the 12%-15% range. Official event is the AES Q3 2025 earnings webcast (aes.com/investors). VERIFICATION: the cited insidermonkey URL and every alternate full-transcript host (theglobeandmail.com, fool.com, seekingalpha.com, investing.com, aol.com, finance.yahoo.com, alphaspread.com, tipranks.com) returned HTTP 403 proxy/policy denials on direct WebFetch, so wording could not be read from the primary page. The figure and framing were corroborated across three independent WebSearch result summaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>C · Stated / regulatory WACC benchmark</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Celsia</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>CELSIA CB</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>company-wide</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>WACC (stated actual) with ROCE</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>WACC 13.02%; ROCE 14.33% (positive differential of 131 bps), FY2022</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>not stated (COP, nominal implied; pre/post-tax not specified)</t>
+        </is>
+      </c>
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>FY2022 results (reported early 2023)</t>
+        </is>
+      </c>
+      <c r="J12" s="29" t="inlineStr">
+        <is>
+          <t>press release</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" s="29" t="inlineStr">
+        <is>
+          <t>Al cierre de 2022, y a pesar del fuerte incremento de las tasas de interés, Celsia mantuvo un diferencial positivo de 131 puntos básicos entre el ROCE de 14,33% frente a un WACC de 13,02%. / EN: At year-end 2022, and despite the sharp rise in interest rates, Celsia maintained a positive differential of 131 basis points between a ROCE of 14.33% and a WACC of 13.02%.</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="inlineStr">
+        <is>
+          <t>https://www.celsia.com/es/noticias/resultados-de-celsia-en-2022/</t>
+        </is>
+      </c>
+      <c r="O12" s="29" t="inlineStr">
+        <is>
+          <t>Celsia FY2022 results press release ('Resultados de Celsia en 2022'). Figures (ROCE 14.33% vs WACC 13.02%, +131 bps) confirmed via WebSearch snippet of this exact official URL; direct WebFetch blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>C · Stated / regulatory WACC benchmark</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>AXIA (ex-Eletrobras)</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>AXIA3 BZ</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>transmission</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>regulated (RAB) WACC</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>7.89% real, after taxes (2025 ANEEL transmission/generation regulatory cycle); ~12.12% pre-tax real (i.e., IPCA + ~12.12%)</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>post-tax AND real (regulatory WACC as defined by ANEEL); currency BRL; applied over an IPCA-indexed regulatory remuneration base (RAB), so effectively IPCA + ~12.12% on a pre-tax basis. Now confirmed as a REAL after-tax rate (the draft had left real/nominal ambiguous).</t>
+        </is>
+      </c>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>ANEEL 2025 tariff cycle (rate in effect from 1 March 2025; superseded by 8.00% from 1 March 2026 per ANEEL's March 2026 WACC update)</t>
+        </is>
+      </c>
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>regulatory filing</t>
+        </is>
+      </c>
+      <c r="K13" s="30" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="L13" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" s="29" t="inlineStr">
+        <is>
+          <t>PT (paraphrase of ANEEL communication, via poder360/cenarioenergia): 'A taxa regulatoria real apos impostos foi definida em 8,10% para o segmento de distribuicao e 8,00% para transmissao e geracao. Antes dos impostos, os percentuais chegam a 12,28% e 12,11%, respectivamente. Em relacao ao ciclo anterior, houve aumento de 0,07 ponto percentual no WACC aplicado a distribuicao e de 0,11 ponto percentual para transmissao e geracao.' EN: 'The real after-tax regulatory rate was set at 8.10% for distribution and 8.00% for transmission and generation. Pre-tax, the percentages reach 12.28% and 12.11% respectively. Versus the previous cycle, there was an increase of 0.07pp for distribution and 0.11pp for transmission and generation.' [Implies prior/2025 transmission WACC = 8.00% - 0.11pp = 7.89% real after-tax.] Note: I could not open ANEEL's page directly (HTTP 403 via WebFetch); text is from WebSearch summaries of the official ANEEL release and Brazilian energy press.</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/aneel/pt-br/assuntos/noticias/2026/aneel-atualiza-taxa-regulatoria-de-remuneracao-do-capital-wacc-regulatorio</t>
+        </is>
+      </c>
+      <c r="O13" s="29" t="inlineStr">
+        <is>
+          <t>Official ANEEL (Brazilian electricity regulator) communication on the regulatory WACC. The March 2026 update sets transmission/generation regulatory WACC at 8.00% real after-tax (12.11% pre-tax), described as a +0.11 percentage-point increase over the prior (2025) cycle, which therefore was 7.89% real after-tax. Sector-wide value applying to all Brazilian transmission concessionaires including AXIA/Eletrobras transmission and Law 12.783/13 quota-regime assets. Corroborated by poder360.com.br and cenarioenergia.com.br coverage. NOTE: this is a sector-wide REGULATORY WACC set by the regulator, not an internal investment hurdle chosen by the company; included as the benchmark ANEEL WACC that AXIA's own materials reference (AXIA Q4 2025 investor slides describe its regulated transmission WACC as 'IPCA + 12.12%').</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>C · Stated / regulatory WACC benchmark</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>AXIA (ex-Eletrobras)</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>AXIA3 BZ</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>transmission</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>regulated (RAB) return / WACC</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>ANEEL-defined regulatory WACC for Law 12.783/13 assets (transmission, quota-regime hydro, Eletronuclear); no company-specific percentage stated in the Eletrobras SEC disclosure itself</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="inlineStr">
+        <is>
+          <t>ANEEL regulatory WACC (real, after taxes per ANEEL methodology); the Eletrobras SEC filing text located did not itself restate pre/post-tax, real/nominal, or currency. Methodology set by ANEEL Resolution 874/2020 (WACC methodology) / REN 918/2021 (calculation procedure for Law 12.783/13 concessions).</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>recurring disclosure in Eletrobras SEC filings (Form 20-F and quarterly 6-K market-letter annexes, 2021-2022)</t>
+        </is>
+      </c>
+      <c r="J14" s="29" t="inlineStr">
+        <is>
+          <t>regulatory filing</t>
+        </is>
+      </c>
+      <c r="K14" s="30" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L14" s="30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M14" s="29" t="inlineStr">
+        <is>
+          <t>Reconstructed (NOT independently verified at the SEC page, which returned 403): 'Compensation for transmission concessions is determined through WACC, the weighted average cost of capital, defined by ANEEL... Resolution No. 874/2020 established the WACC to be applied to the investment for (i) transmission assets, hydroelectric plants subject to the physical guarantee and power quota regime (Law No. 12,783/13), and (ii) Eletronuclear.'</t>
+        </is>
+      </c>
+      <c r="N14" s="31" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1439124/000129281421001692/ebr20210422_6k.htm</t>
+        </is>
+      </c>
+      <c r="O14" s="29" t="inlineStr">
+        <is>
+          <t>Eletrobras Form 6-K market-letter annex / Form 20-F, transmission concession compensation and regulatory framework section. COULD NOT be opened for page-level verification: SEC.gov returned HTTP 403 to WebFetch on every attempt. The substance is corroborated: ANEEL Resolution 874/2020 approving the updated WACC methodology (2020) and REN 918/2021 defining WACC for Law 12.783/13 transmission and quota-regime generation (incl. Eletronuclear) are confirmed via ANEEL/press sources. This is a regulator-set RAB WACC, not an internal company hurdle, and no specific percentage appears in the company disclosure located.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>D · Third-party estimate (not company-stated)</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Engie Brasil / ENGIE</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>EGIE3 BZ</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>transmission</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>IRR (real, project-level, third-party estimate)</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>~7-8% real IRR estimated for ENGIE's winning lots in ANEEL Transmission Auction 01/2026 (analyst estimate); described by analysts as modest / below the sector historical average</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>Real; project/asset-level IRR; pre/post-tax not stated; BRL. This is an analyst-estimated achieved return on new regulated (transmission) capex, NOT a company-stated hurdle. Deságio médio (average discount) on the lots reported at ~53%.</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>March 2026 (post-auction analyst commentary)</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>third-party analyst/press (Guia do Investidor; also InfoMoney, Acionista, ADVFN)</t>
+        </is>
+      </c>
+      <c r="K15" s="34" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M15" s="33" t="inlineStr">
+        <is>
+          <t>Per analyst commentary summarized in Brazilian press (WebSearch): 'os projetos podem entregar TIR real entre 7% e 8%, o que e considerado modesto para o setor' / 'the projects may deliver a real IRR between 7% and 8%, considered modest for the sector'. [Portuguese source with English translation; third-party, paraphrased/snippet-level, not page-level verbatim]</t>
+        </is>
+      </c>
+      <c r="N15" s="35" t="inlineStr">
+        <is>
+          <t>https://guiadoinvestidor.com.br/mercado/engie-egie3-leva-leilao-da-aneel-mas-retorno-decepciona-e-acende-alerta-no-mercado/</t>
+        </is>
+      </c>
+      <c r="O15" s="33" t="inlineStr">
+        <is>
+          <t>Brazilian financial press reporting analyst estimates of real IRR on ENGIE's 2026 transmission auction lots (lot 2 and sub-lots 3A-3D via ENGIE Transmissao de Energia Participacoes, ~R$1.6bn capex, RAP ~R$122.7m). Third-party, not company-disclosed. Included only as a directional benchmark of the returns ENGIE is accepting on new regulated transmission capex. Article confirmed live via WebSearch (page body could not be opened via WebFetch due to egress-policy 403).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>D · Third-party estimate (not company-stated)</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Grupo Energía Bogotá</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>GEB CB</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>group-level</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>sell-side analyst valuation WACC for GEB business units (third-party, NOT company-stated)</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>~10.3% (attributed to 2024 valuation, UNVERIFIED); ~11.3% average for 2023 (corroborated), with ~10.4% for Enel Colombia</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>not stated (Beta 0.55x for energy companies; gas-distribution beta reported as 0.83x for the 2023 exercise — draft's '0.7x' could not be corroborated)</t>
+        </is>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>Davivienda Corredores 'Zoom a las Empresas – GEB' (2023 edition corroborated; 2024 edition figure of ~10.3% not independently verifiable)</t>
+        </is>
+      </c>
+      <c r="J16" s="33" t="inlineStr">
+        <is>
+          <t>investor presentation</t>
+        </is>
+      </c>
+      <c r="K16" s="34" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="L16" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M16" s="33" t="inlineStr">
+        <is>
+          <t>"...un WACC promedio de 11.3% para las unidades de TGI, Cálidda, Dunas, Transmisión y Gebbras, dejando con un WACC de 10.4% a Enel Colombia" with "...una Beta (u) de 0.55x para compañías de energía y 0.83x para compañías de distribución de gas" ("...an average WACC of 11.3% for the TGI, Cálidda, Dunas, Transmisión and Gebbras units, leaving Enel Colombia with a WACC of 10.4%"; Beta of 0.55x for energy companies and 0.83x for gas-distribution companies). Paraphrased from Davivienda Corredores 'Zoom a las Empresas – GEB'; exact page text not directly retrievable (HTTP 403). The ~10.3%/2024 figure in the draft was not corroborated.</t>
+        </is>
+      </c>
+      <c r="N16" s="35" t="inlineStr">
+        <is>
+          <t>https://libro.daviviendacorredores.com/2023/zoom-a-empresas/geb/</t>
+        </is>
+      </c>
+      <c r="O16" s="33" t="inlineStr">
+        <is>
+          <t>THIRD-PARTY / SELL-SIDE ANALYST report (Davivienda Corredores), not a GEB official disclosure. Corroborated figures (via search summaries; direct fetch 403): an ~11.3% average WACC applied to TGI, Cálidda, Dunas, Transmisión and Gebbras, and ~10.4% for Enel Colombia, with a Beta of 0.55x for energy companies and 0.83x for gas-distribution companies — these appear in the 2023 exercise. The draft's specific claim of ~10.3% for 2024 (down from 11.3%) and a 0.7x gas-distribution beta could NOT be independently corroborated; both the 2023 and 2024 Davivienda pages returned HTTP 403. This is an analyst's valuation WACC, not confirmed verbatim from GEB's own Reporte Integrado or estados financieros (GEB official pages also 403).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>D · Third-party estimate (not company-stated)</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Empresa Eléctrica Pehuenche</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>PEHUEN CI</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>group-level</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>WACC (third-party computed, ultimate-parent level)</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>~8.0-8.8% (post-tax, nominal, USD; analyst-computed)</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="33" t="inlineStr">
+        <is>
+          <t>post-tax, nominal; USD; analyst-computed (not stated by the company)</t>
+        </is>
+      </c>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>as of 2026 (third-party data services)</t>
+        </is>
+      </c>
+      <c r="J17" s="33" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="K17" s="34" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="L17" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M17" s="33" t="inlineStr">
+        <is>
+          <t>GuruFocus: 'Enel Chile WACC %: 8.8%'. AlphaSpread: 'Enel Chile's current Cost of Equity is 8.85%, while its WACC stands at 8.08%; cost of debt is 6.84%.' [Third-party analyst-computed WACC, not a company-stated hurdle rate; grandparent/group level, not gas-specific.]</t>
+        </is>
+      </c>
+      <c r="N17" s="35" t="inlineStr">
+        <is>
+          <t>https://www.gurufocus.com/term/wacc/NYSE:ENIC/WACC-/Enel-Chile</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="inlineStr">
+        <is>
+          <t>GuruFocus / AlphaSpread WACC pages for Enel Chile SA (ENIC), the ultimate listed parent of Pehuenche via Enel Generacion Chile. GuruFocus: WACC 8.8%; AlphaSpread: WACC ~8.08%, cost of equity ~8.85%, cost of debt ~6.84%, debt weight ~38%. This is a computed figure, NOT a company-disclosed hurdle rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>A · Gas-specific — a rate explicitly tied to gas-fired generation or gas infrastructure.</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="36" t="n"/>
+      <c r="N20" s="36" t="n"/>
+      <c r="O20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle — a target IRR or minimum spread over WACC the company applies to investments/PPAs (mostly renewables/portfolio-wide; none gas-specific).</t>
+        </is>
+      </c>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="M21" s="36" t="n"/>
+      <c r="N21" s="36" t="n"/>
+      <c r="O21" s="37" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>C · Stated / regulatory WACC — a company-stated actual WACC, or the regulator-set (RAB) WACC the company earns on regulated assets.</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="36" t="n"/>
+      <c r="N22" s="36" t="n"/>
+      <c r="O22" s="37" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>D · Third-party estimate — analyst / data-vendor computed figures; NOT company-stated. Included only as directional context.</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="36" t="n"/>
+      <c r="N23" s="36" t="n"/>
+      <c r="O23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>'Official?' = Official means from the company or its controlling parent/group; the regulatory-WACC rows are set by the regulator (ANEEL/CREG), noted in Source detail.</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="36" t="n"/>
+      <c r="N24" s="36" t="n"/>
+      <c r="O24" s="37" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A21:O21"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId14"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Coverage &amp; gaps — what was found, and what the egress policy prevented (do not treat blocked = 'no disclosure')</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Blocked official domains</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>What a human with browser access should check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="96" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ENEV3 BZ</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Eneva</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>BLOCKED — likely has data</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Brazil's gas-to-power pure-play; the single most likely to disclose a gas IRR. Third parties reference an 'Unlevered IRR of Projects' slide in Eneva's corporate presentation showing per-project unlevered IRRs (Azulão-Jaguatirica, Parnaíba V). XP research characterises Eneva's realised returns as &gt;20% real IRR since 2017 (a track record, not a stated hurdle).</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>api.mziq.com; ri.eneva.com.br; rad.cvm.gov.br; earnings-call transcript hosts</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>The current Eneva corporate presentation 'Unlevered IRR of Projects' slide; Formulário de Referência; and the DFP/ITR impairment notes (value-in-use 'taxa de desconto'/WACC for the thermal &amp; E&amp;P units) — the most likely official WACC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>COLBUN CI</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>BLOCKED — none surfaced</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
+        <is>
+          <t>Disclosure is framed around CapEx guidance and project pipeline, not explicit return thresholds. Management stated BESS projects are always linked to a PPA (i.e. not merit-order/spread bets). No target IRR/WACC/spread found in search snippets.</t>
+        </is>
+      </c>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>www.colbun.cl (all corporate/IR pages &amp; PDFs)</t>
+        </is>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>Memoria Integrada / annual report; earnings-call transcripts; bond prospectus (impairment discount rate); any Investor Day deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>AURE3 BZ</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Auren Energia</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>None disclosed</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>3rd-largest Brazilian generator, 100% renewable (hydro + wind/solar) + trading, ~no gas — so no gas/thermal hurdle exists. No company-stated hurdle/target IRR/WACC found; all WACC/IRR figures located were third-party.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>ri.aurenenergia.com.br; api.mziq.com; rad.cvm.gov.br</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Audited financial statements: impairment / value-in-use discount rate (the most likely place a company discount rate is disclosed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>ENLASA CI</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Energía Latina (Enlasa)</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>None disclosed</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>Small backup/peaking diesel-&amp;-gas generator; does not publish investor-day-style return frameworks. Only bond-line mechanics and rating narrative surfaced (Category AA; EBITDA floor ~US$10m).</t>
+        </is>
+      </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>enlasa.com; cmfchile.cl; humphreys.cl</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>CMF bond prospectus and Memoria/Estados Financieros — any impairment 'tasa de descuento'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>EGIE3 BZ</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Engie Brasil</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Found (group-level)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>The listed Brazilian entity does not state its own hurdle; the ENGIE group applies an IRR-minus-WACC spread of ~150–250 bps plus an NPV/Capex value-creation test. Captured on the findings tab.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>engie.com PDF (page-level verbatim blocked)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>ENGIE group H1/FY results transcripts &amp; fact sheets; Engie Brasil Formulário de Referência for any local WACC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>ENELGXCH CI</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Enel Generación Chile</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>Found (parent/group)</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t>Hurdle stated at Enel Chile / Enel group level (≥300 bps above WACC for BESS; ~300 bps IRR-WACC for renewables). Renewables/storage-specific, explicitly not gas. Captured on the findings tab.</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>enel.com; enelamericas.com; transcript hosts (verbatim blocked)</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="inlineStr">
+        <is>
+          <t>Enel Chile Q1 2026 call transcript; Enel 2025–2027 Strategic Plan deck for the exact renewables IRR-WACC slide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CELSIA CB</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Celsia</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Found (company-wide)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Company-wide ROCE target &gt;200 bps above WACC; actual FY2022 WACC 13.02% / ROCE 14.33%. Not gas-specific though Celsia owns gas thermal. Captured on the findings tab.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>www.celsia.com (verbatim blocked; quotes from search snippets)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>'¿Por qué invertir en Celsia?' IR page; Informe Integrado; results releases — for the current ROCE/WACC figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>GEB CB</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Grupo Energía Bogotá</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>Found (gas transport)</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>Gas-transport regulated WACC 11.88% (pre-tax, real, constant COP), set by CREG for TGI — a genuine gas-infrastructure return, though regulator-set, not GEB's own hurdle. Rolled back / refund ordered by CREG in Mar-2026. Captured on the findings tab.</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>creg.gov.co; gestornormativo.creg.gov.co; GEB IR pages</t>
+        </is>
+      </c>
+      <c r="F10" s="39" t="inlineStr">
+        <is>
+          <t>Primary CREG Resolución 102 002 de 2023 &amp; Res. 103 de 2021; GEB Reporte Integrado for any group investment return criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>AXIA3 BZ</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>AXIA (ex-Eletrobras)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Found (regulatory WACC)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>No internal hurdle found; sells mostly hydro. Its regulated transmission earns the ANEEL WACC ~7.89% real after-tax (2025; 8.00% from Mar-2026); AXIA slides describe it as 'IPCA + 12.12%'. Captured on the findings tab.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>sec.gov (20-F/6-K); aneel.gov.br pages (verbatim blocked)</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>AXIA Business/Strategic Plan and Q4 2025 investor slides for any project return target; ANEEL WACC releases for the exact regulatory rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>AESO3 BZ</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>AES Brasil / AES Corp</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Found (group-level)</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>AES (parent) targets 12–15% unlevered returns on renewable/PPA investments (data-center PPAs at the higher end). The one gas-specific figure (Uruguaiana 7.16% regulatory return) is ANEEL-set and the plant was divested in 2020. Captured on the findings tab.</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>aes.com; transcript hosts (verbatim blocked)</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>AES Corp Q3 2025 call transcript; AES Brasil reference form. Note gas thermal was largely divested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PEHUEN CI</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Empresa Eléctrica Pehuenche</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>None (third-party only)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Hydro subsidiary of Enel Generación Chile; no own disclosure. Only third-party WACC for the ultimate parent Enel Chile (~8.0–8.8%) exists. No gas.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>(subsidiary — relies on Enel group disclosure)</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Enel Chile group materials (see ENELGXCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>ENMT4 BZ</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Energisa Mato Grosso</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>N/A — distribution</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Electricity distribution utility, not a generator. Its regulated return is the ANEEL distribution WACC (~8.10% real after-tax, 2026). No generation/gas hurdle.</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>energisa.com.br / api.mziq (not pursued — N/A)</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>ANEEL distribution WACC releases if the regulated return is of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>EQMA3B BZ</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Equatorial Maranhão</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>N/A — distribution</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Electricity distribution utility, not a generator. Regulated by the ANEEL distribution WACC. No generation/gas hurdle.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>equatorialenergia.com.br (not pursued — N/A)</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Equatorial group investor materials for any group project hurdle (not gas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>GEPA4 BZ</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Rio Paranapanema</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>None — hydro</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>100% hydro; no gas. No company-stated hurdle found.</t>
+        </is>
+      </c>
+      <c r="E16" s="39" t="inlineStr">
+        <is>
+          <t>(not disclosed)</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="inlineStr">
+        <is>
+          <t>Reference form / results, if any group return target exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>PRMN3B BZ</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>None — single hydro asset</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Single hydro plant (Manso); no gas; no investor-return framework published.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>(not disclosed)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Reference form, if any.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>CEBR5 BZ</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>None — ex-utility</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Hollowed-out ex-utility that sold most generation; no gas hurdle published.</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>(not disclosed)</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>Reference form / results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="96" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>PUNTILLA CI</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Eléctrica Puntilla</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>None — small hydro</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Small run-of-river hydro (Chile); no gas; no return framework published.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>(not disclosed)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>CMF Memoria, if any.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="96" customHeight="1">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>WIG JA</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Wigton Energy</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>None — wind</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Wind operator (Jamaica); no gas; no stated investment hurdle found.</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>(not disclosed)</t>
+        </is>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>JSE annual report, if any return target.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LatAm_Power_Companies_Research.xlsx
+++ b/LatAm_Power_Companies_Research.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Notes &amp; Verification" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Key Sources" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Gas &amp; Investment Hurdle Rates" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Hurdle Rates - Coverage &amp; Gaps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Eneva Project IRRs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Hurdle Rates - Coverage &amp; Gaps" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -199,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -312,6 +313,22 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9440,7 +9457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9467,10 +9484,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="74" customHeight="1">
+    <row r="2" ht="88" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Key finding: NO company in this list publishes a clean gas-fired-generation IRR hurdle the way NRG/Vistra/RWE/AGL do. Closest data points below. NOTE: the two most gas-relevant names (Eneva, Colbún) could not be fully checked — this environment's network egress policy blocks their official domains (api.mziq.com, colbun.cl). See the 'Coverage &amp; Gaps' tab. Every quote here was captured via web-search of official sources; direct fetches of many official PDFs were 403-blocked, so page-level verbatim was often unavailable (noted per row).</t>
+          <t>Key finding: NO company in this list publishes a single gas-fired-generation IRR *hurdle* the way NRG/Vistra/RWE/AGL do. The CLOSEST — and best gas data point — is ENEVA, which discloses per-project REAL IRRs benchmarked as a spread over the NTN-b 2040 real risk-free rate (top rows; full breakdown on the 'Eneva Project IRRs' tab, from the April-2026 deck you provided). Others disclose a spread-over-WACC or a portfolio target IRR. Colbún's official domain remains blocked by this environment's egress policy (see 'Coverage &amp; Gaps'). Non-Eneva quotes were captured via web-search of official sources; many official PDFs were 403-blocked, so page-level verbatim was often unavailable (noted per row).</t>
         </is>
       </c>
     </row>
@@ -9560,27 +9577,27 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Grupo Energía Bogotá</t>
+          <t>Eneva</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>GEB CB</t>
+          <t>ENEV3 BZ</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>gas transport</t>
+          <t>New gas-to-power (2026 Capacity Auction 'LRCAP26' — Sergipe / Ceará / Southeast hubs)</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>regulated (RAB) WACC for gas transport</t>
+          <t>Unlevered IRR (real)</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>11.88% (raised from 10.94%); rate rolled back / refund ordered by CREG in 2026</t>
+          <t>~14%–27% real (Southeast ~14%, Ceará ~22%, Sergipe ~26–27%)</t>
         </is>
       </c>
       <c r="G4" s="22" t="inlineStr">
@@ -9590,17 +9607,17 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>pre-tax (antes de impuestos), real (pesos constantes / constant COP)</t>
+          <t>Unlevered, real (IPCA-linked), BRL. Shown as a spread over NTN-b 2040 (real risk-free). 'Unlevered IRR given projects have not begun financing.' LRCAP26 capex R$18.2bn.</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Resolución CREG 102 002 de 2023 (approved CREG session 1271, 2 June 2023). Base rate/methodology: Resolución CREG 103 de 2021 (10.94% en pesos constantes antes de impuestos). CORRECTION: draft cited 'CREG 004/175 de 2021' as the base — the 10.94% base rate is actually from Resolución CREG 103 de 2021 (Res. 175 de 2021 is a separate general remuneration methodology).</t>
+          <t>April 2026 (as of Mar-26)</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>regulatory filing</t>
+          <t>investor presentation</t>
         </is>
       </c>
       <c r="K4" s="22" t="inlineStr">
@@ -9615,49 +9632,49 @@
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t>"...un incremento en la tasa de descuento del costo de capital (WACC), que pasó de 10,94% a 11,88% en 2023 mediante la Resolución CREG 102 002, permitiendo a empresas transportadoras como TGI —filial del Grupo de Energía de Bogotá— incrementar costos en la componente de transporte." / "CREG Resolution 103 of 2021 with a WACC of 10.94% in constant pesos before taxes" ("...an increase in the discount rate / cost of capital (WACC), which went from 10.94% to 11.88% in 2023 via CREG Resolution 102 002, allowing transport companies such as TGI —subsidiary of Grupo de Energía de Bogotá— to increase costs in the transport component"; base rate of 10.94% set by CREG Resolution 103 of 2021, expressed in constant pesos before taxes). Source: Ministerio de Minas y Energía / El Nuevo Siglo / Infobae reporting on the CREG resolutions; primary CREG resolution text not directly retrievable (HTTP 403).</t>
+          <t>'Leveraged Internal Rate of Return (IRR) of Projects (in real terms)'; note (7) 'Unlevered IRR given projects have not begun financing'; 'LRCAP26 Capex R$ 18.2 bi'.</t>
         </is>
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-ordena-devolver-mas-de-150-mil-millones-a-usuarios-de-gas-natural-por-cobros-adicionales-en-transporte/</t>
+          <t>https://ri.eneva.com.br/en/financial-information/presentations-and-conference-calls/</t>
         </is>
       </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>Regulator-set (CREG) WACC applied to gas transport activity, applicable to TGI (GEB's Colombian gas-transport subsidiary) and Promigas. Resolución CREG 102 002 de 2023 raised the tasa de descuento from 10.94% to 11.88% (increase justified by the 35% income-tax rate under Ley 2277 de 2022). Figure corroborated across multiple official/press sources: Ministerio de Minas y Energía, Forbes Colombia, Infobae, El Colombiano, Semana, El Nuevo Siglo. Primary CREG pages (gestornormativo.creg.gov.co originals + htm, suin-juriscol.gov.co) all returned HTTP 403 to automated fetch, so no verbatim pull from the primary CREG document was possible. IMPORTANT: this is a regulator-set RAB return, NOT an investment hurdle rate independently declared by GEB. In March 2026 CREG upheld appeals, ordered the WACC reduced and ~COP 150bn overcharged (2023-present) refunded to users, so the 11.88% rate is rolled back / under dispute.</t>
+          <t>Eneva Corporate Presentation, April 2026, slide 13 ('…With Capital Allocations with Sound Returns…'). File provided by user (official Eneva deck; api.mziq.com host is blocked by this environment's egress policy). IRR %s are approximate — read from the chart (0–30% axis); the deck prints no numeric IRR table.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>A · Gas-specific (regulatory / historical)</t>
+          <t>A · Gas-specific</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>AES Brasil / AES Corp</t>
+          <t>Eneva</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>AESO3 BZ</t>
+          <t>ENEV3 BZ</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>named gas project</t>
+          <t>Existing G2P / thermal / LNG projects (Parnaíba V &amp; VI, Azulão-Jaguatirica, Azulão 950, Small-Scale LNG, Fortaleza TPP, Celse, BTG)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>regulated / regulatory return (ANEEL WACC embedded in the plant's tariff/CVU)</t>
+          <t>Leveraged IRR (real)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>7.16% (described as a real return, already net of taxes)</t>
+          <t>~10%–30% real (e.g. Parnaíba V ~20%, Small-Scale LNG ~24–30%, Azulão-Jaguatirica ~11%)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -9667,42 +9684,42 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>Real, post-tax ('real index foreseen for generators, based on WACC, already discounting taxes'), BRL. This is a regulator-set (ANEEL) WACC used in the Uruguaiana gas-fired thermal plant's variable-cost/tariff (CVU) calculation, NOT a hurdle rate stated by AES. In the underlying 2015 dispute the generator had applied a 10% rate and ANEEL imposed 7.16%, so 7.16% is ANEEL's figure, expressly not AES's own return expectation. Levered/unlevered: not stated (regulatory WACC).</t>
+          <t>Leveraged, real (IPCA-linked), BRL; shown as spread over NTN-b 2040. Project-level leverage 46%–85% of capex; avg debt cost IPCA+3.1% to +7.0% (printed on slide). Fortaleza TPP unleveraged at acquisition.</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>ANEEL determination for the AES Uruguaiana gas-fired thermal plant; the 7.16% vs 10% dispute references February 2015. Plant divested by AES in 2020. Exact determination date not confirmed from an official AES source.</t>
+          <t>April 2026 deck (projects Dec-18 → Nov-24)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>news (reporting an ANEEL regulatory determination) — third party</t>
+          <t>investor presentation</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>Third-party</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>Per the source summary (Portuguese, translated): the 7.16% 'is the real index foreseen for generators, based on the calculation of WACC (weighted average cost of capital), already discounting taxes; the CVU was calculated based on a regulatory return rate of 7.16% per year' — versus the 10% rate the generator had applied. Full primary-page verbatim not accessible (page 403-blocked); wording confirmed via WebSearch summary.</t>
+          <t>Printed on slide 13 — Project Level Leverage (%capex): 56 / 59 / 46 / 85 / 66 / n.a. / on-going / n.a. / 9. Avg Cost (IPCA+): 3.1% / 3.3% / 4.4% / 5.8% / 3.4% / n.a. / 4.1% / 7.0% / 6.9%. See the 'Eneva Project IRRs' tab.</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>https://www.canalenergia.com.br/noticias/4931313/aneel-mantem-taxa-de-retorno-de-uruguaiana-em-716</t>
+          <t>https://ri.eneva.com.br/en/financial-information/presentations-and-conference-calls/</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
-          <t>CanalEnergia article 'Aneel mantem taxa de retorno de Uruguaiana em 7,16%'. Reports ANEEL keeping the regulatory return for the Uruguaiana gas thermal plant at 7.16% (real, WACC-based, net of taxes) in the CVU calculation, over the generator's applied 10% rate. The CanalEnergia page returned a 403 proxy denial on direct WebFetch; wording confirmed via WebSearch result summary. Third-party source; regulator-set figure, not AES's own investment hurdle; AES/AES Brasil divested Uruguaiana in 2020.</t>
+          <t>Eneva Corporate Presentation, April 2026, slide 13 ('…With Capital Allocations with Sound Returns…'). File provided by user (official Eneva deck; api.mziq.com host is blocked by this environment's egress policy). IRR %s are approximate — read from the chart (0–30% axis); the deck prints no numeric IRR table.</t>
         </is>
       </c>
     </row>
@@ -9714,27 +9731,27 @@
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Enel Generación Chile</t>
+          <t>Eneva</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>ENELGXCH CI</t>
+          <t>ENEV3 BZ</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>renewables (standalone battery storage / BESS)</t>
+          <t>Company-wide capital-allocation discipline</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>spread over WACC</t>
+          <t>Spread over NTN-b 2040 (real risk-free)</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>at least +300 bps above WACC (&gt;=300 basis points spread)</t>
+          <t>Positive real spread over NTN-b 2040 (~6–9% real over the period); no single numeric hurdle stated</t>
         </is>
       </c>
       <c r="G6" s="26" t="inlineStr">
@@ -9744,17 +9761,17 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>not stated (spread over the company's WACC; pre/post-tax and real/nominal not specified; currency not specified). This is storage/BESS-specific, explicitly NOT gas.</t>
+          <t>Real, BRL; benchmark = NTN-b 2040 (IPCA-linked Treasury). Eneva presents returns as a spread over the real risk-free rate rather than a fixed hurdle %.</t>
         </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
         <is>
-          <t>Enel Chile Q1 2026 earnings call, late April 2026 (call/results reported ~29 Apr - 4 May 2026)</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="J6" s="25" t="inlineStr">
         <is>
-          <t>earnings call transcript</t>
+          <t>investor presentation</t>
         </is>
       </c>
       <c r="K6" s="26" t="inlineStr">
@@ -9764,176 +9781,176 @@
       </c>
       <c r="L6" s="26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
         <is>
-          <t>As reported consistently across transcripts of the official call: management stated the company advances standalone BESS projects only when returns are "at least 300 basis points above our WACC," and stress-tests them against more critical/stressed market scenarios. (Related: standalone BESS can be profitable, with higher profitability when the BESS is used to hybridize an existing power plant.) Exact primary-webcast wording could not be independently read due to proxy egress blocking (403).</t>
+          <t>Slide 13 y-axis 'Spread to NTN-b 2040'; white benchmark line 'NTN-b 2040' — note (8) 'Brazilian Treasury Bond linked to Brazilian Consumer Prices Inflation Variation (IPCA Index)'.</t>
         </is>
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
-          <t>https://www.insidermonkey.com/blog/enel-chile-s-a-nyseenic-q1-2026-earnings-call-transcript-1753951/</t>
+          <t>https://ri.eneva.com.br/en/financial-information/presentations-and-conference-calls/</t>
         </is>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
-          <t>Enel Chile S.A. (NYSE:ENIC; intermediate parent of the listed entity Enel Generacion Chile) Q1 2026 earnings call, management remarks on standalone battery storage (BESS) capital allocation. Stated at the Enel Chile parent level, not at the listed entity Enel Generacion Chile. Verbatim wording corroborated identically across multiple independent transcript aggregators (Insider Monkey, Investing.com, Yahoo Finance highlights, AlphaSpread, Benzinga). The originally cited Seeking Alpha URL (article/4897916) could not be located in searches and is replaced here with a corroborated transcript page. All transcript pages and the official Enel Chile webcast return 403 at the agent proxy gateway (CONNECT policy denial), so the primary webcast/official transcript was not directly read.</t>
+          <t>Eneva does not publish a single hurdle-rate %; it benchmarks each project's real IRR against the NTN-b 2040 real risk-free rate. Eneva Corporate Presentation, April 2026, slide 13 ('…With Capital Allocations with Sound Returns…'). File provided by user (official Eneva deck; api.mziq.com host is blocked by this environment's egress policy). IRR %s are approximate — read from the chart (0–30% axis); the deck prints no numeric IRR table.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>B · Investment hurdle (spread / target IRR)</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>Enel Generación Chile</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>ENELGXCH CI</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>renewables (group Renewables business under Enel SpA plan)</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>spread over WACC</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
-        <is>
-          <t>~300 bps average IRR-WACC spread targeted for new (renewables) projects</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="inlineStr">
-        <is>
-          <t>not stated (average spread of project IRR over WACC; pre/post-tax and real/nominal not specified; group reports in EUR). Applies to the group Renewables business, not gas/thermal.</t>
-        </is>
-      </c>
-      <c r="I7" s="25" t="inlineStr">
-        <is>
-          <t>Capital Markets Day, 19-22 Nov 2024 (2025-2027 Strategic Plan)</t>
-        </is>
-      </c>
-      <c r="J7" s="25" t="inlineStr">
-        <is>
-          <t>investor presentation</t>
-        </is>
-      </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>A · Gas-specific</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Grupo Energía Bogotá</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>GEB CB</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>gas transport</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>regulated (RAB) WACC for gas transport</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>11.88% (raised from 10.94%); rate rolled back / refund ordered by CREG in 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>pre-tax (antes de impuestos), real (pesos constantes / constant COP)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>Resolución CREG 102 002 de 2023 (approved CREG session 1271, 2 June 2023). Base rate/methodology: Resolución CREG 103 de 2021 (10.94% en pesos constantes antes de impuestos). CORRECTION: draft cited 'CREG 004/175 de 2021' as the base — the 10.94% base rate is actually from Resolución CREG 103 de 2021 (Res. 175 de 2021 is a separate general remuneration methodology).</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>regulatory filing</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Official</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
-        <is>
-          <t>As reported from Enel's official 2025-2027 Strategic Plan materials: the group Renewables business targets an approximately "300 bps average spread between IRR and WACC" for new projects (Enel Americas states the same ~300 bps average IRR-WACC spread for new generation projects). Exact slide text could not be independently read due to proxy egress blocking the enel.com PDF (403).</t>
-        </is>
-      </c>
-      <c r="N7" s="27" t="inlineStr">
-        <is>
-          <t>https://www.enel.com/content/dam/enel-com/documenti/investitori/informazioni-finanziarie/2024/2025-2027-strategic-plan.pdf</t>
-        </is>
-      </c>
-      <c r="O7" s="25" t="inlineStr">
-        <is>
-          <t>Enel SpA (ultimate controlling group) 2025-2027 Strategic Plan / Capital Markets Day presentation. CORRECTION vs draft: the ~300 bps average IRR-WACC spread is specifically the target for the group RENEWABLES business (mirrored in Enel Americas' 2025-2027 generation plan), NOT a blanket group-wide-across-all-businesses metric as the draft implied by labeling it 'group-level'. Stated at Enel SpA group level for the renewables/generation business, not at Enel Chile or Enel Generacion Chile. The official enel.com PDF and enelamericas.com annexes return 403 at the proxy gateway; the figure and its renewables attribution are corroborated across multiple independent summaries of the official plan.</t>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>"...un incremento en la tasa de descuento del costo de capital (WACC), que pasó de 10,94% a 11,88% en 2023 mediante la Resolución CREG 102 002, permitiendo a empresas transportadoras como TGI —filial del Grupo de Energía de Bogotá— incrementar costos en la componente de transporte." / "CREG Resolution 103 of 2021 with a WACC of 10.94% in constant pesos before taxes" ("...an increase in the discount rate / cost of capital (WACC), which went from 10.94% to 11.88% in 2023 via CREG Resolution 102 002, allowing transport companies such as TGI —subsidiary of Grupo de Energía de Bogotá— to increase costs in the transport component"; base rate of 10.94% set by CREG Resolution 103 of 2021, expressed in constant pesos before taxes). Source: Ministerio de Minas y Energía / El Nuevo Siglo / Infobae reporting on the CREG resolutions; primary CREG resolution text not directly retrievable (HTTP 403).</t>
+        </is>
+      </c>
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-ordena-devolver-mas-de-150-mil-millones-a-usuarios-de-gas-natural-por-cobros-adicionales-en-transporte/</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>Regulator-set (CREG) WACC applied to gas transport activity, applicable to TGI (GEB's Colombian gas-transport subsidiary) and Promigas. Resolución CREG 102 002 de 2023 raised the tasa de descuento from 10.94% to 11.88% (increase justified by the 35% income-tax rate under Ley 2277 de 2022). Figure corroborated across multiple official/press sources: Ministerio de Minas y Energía, Forbes Colombia, Infobae, El Colombiano, Semana, El Nuevo Siglo. Primary CREG pages (gestornormativo.creg.gov.co originals + htm, suin-juriscol.gov.co) all returned HTTP 403 to automated fetch, so no verbatim pull from the primary CREG document was possible. IMPORTANT: this is a regulator-set RAB return, NOT an investment hurdle rate independently declared by GEB. In March 2026 CREG upheld appeals, ordered the WACC reduced and ~COP 150bn overcharged (2023-present) refunded to users, so the 11.88% rate is rolled back / under dispute.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>B · Investment hurdle (spread / target IRR)</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Engie Brasil / ENGIE</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>EGIE3 BZ</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>group-level</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>spread over WACC (IRR minus WACC)</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>IRR minus WACC spread of at least 150-250 bps (reference ~200 bps), accompanied by an NPV/Capex value-creation criterion of ~20-25%</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="inlineStr">
-        <is>
-          <t>Not stated precisely. ENGIE group applies technology- and contract-differentiated WACCs; the portfolio is designed to deliver group WACC + ~200 bps. Pre/post-tax, real vs nominal and currency not specified by the company. NOTE: this is a controlling-parent (ENGIE SA, Paris-listed) group framework, NOT a figure stated by the Brazilian listed entity Engie Brasil Energia (EGIE3).</t>
-        </is>
-      </c>
-      <c r="I8" s="25" t="inlineStr">
-        <is>
-          <t>Reiterated at ENGIE group H1 2025 results (1 August 2025); framework set out earlier at ENGIE Capital Markets Day / investor updates (2023-2025)</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="inlineStr">
-        <is>
-          <t>earnings call transcript / investor presentation (group-level, controlling parent ENGIE SA)</t>
-        </is>
-      </c>
-      <c r="K8" s="26" t="inlineStr">
-        <is>
-          <t>Official</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t>Corroborated across multiple WebSearch results of official ENGIE documents (primary PDF could not be opened in this environment due to an egress-policy 403): ENGIE requires investments to match or exceed an IRR minus WACC spread of at least 150 to 250 basis points (reference ~200 bps), together with an NPV/Capex ratio of roughly 20-25%. [English; corroborated by search snippets of the ENGIE H1 2025 transcript and fact sheets, but not a page-level verified verbatim quote]</t>
-        </is>
-      </c>
-      <c r="N8" s="27" t="inlineStr">
-        <is>
-          <t>https://www.engie.com/sites/default/files/assets/documents/2025-08/ENGIE%20H1%202025%20-%20Transcript.pdf</t>
-        </is>
-      </c>
-      <c r="O8" s="25" t="inlineStr">
-        <is>
-          <t>ENGIE SA (Paris-listed controlling parent) H1 2025 results transcript, capital-allocation/investment-discipline section. Canonical IR path (dated 2025-08) verified as a live official URL via WebSearch; an equivalent mirror exists at https://www.engie.com/app/uploads/2026/03/ENGIE-H1-2025-Transcript.pdf (the URL cited in the original draft). The 150-250 bps IRR-WACC spread plus ~20-25% NPV/Capex criterion is corroborated by multiple official ENGIE documents (H1 2025 transcript and fact sheets). GROUP LEVEL, not the Brazilian listed entity. Page-level verbatim could not be extracted (see verification_notes: WebFetch blocked by egress policy).</t>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>A · Gas-specific (regulatory / historical)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>AES Brasil / AES Corp</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>AESO3 BZ</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>named gas project</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>regulated / regulatory return (ANEEL WACC embedded in the plant's tariff/CVU)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>7.16% (described as a real return, already net of taxes)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>Real, post-tax ('real index foreseen for generators, based on WACC, already discounting taxes'), BRL. This is a regulator-set (ANEEL) WACC used in the Uruguaiana gas-fired thermal plant's variable-cost/tariff (CVU) calculation, NOT a hurdle rate stated by AES. In the underlying 2015 dispute the generator had applied a 10% rate and ANEEL imposed 7.16%, so 7.16% is ANEEL's figure, expressly not AES's own return expectation. Levered/unlevered: not stated (regulatory WACC).</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>ANEEL determination for the AES Uruguaiana gas-fired thermal plant; the 7.16% vs 10% dispute references February 2015. Plant divested by AES in 2020. Exact determination date not confirmed from an official AES source.</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>news (reporting an ANEEL regulatory determination) — third party</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>Per the source summary (Portuguese, translated): the 7.16% 'is the real index foreseen for generators, based on the calculation of WACC (weighted average cost of capital), already discounting taxes; the CVU was calculated based on a regulatory return rate of 7.16% per year' — versus the 10% rate the generator had applied. Full primary-page verbatim not accessible (page 403-blocked); wording confirmed via WebSearch summary.</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>https://www.canalenergia.com.br/noticias/4931313/aneel-mantem-taxa-de-retorno-de-uruguaiana-em-716</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>CanalEnergia article 'Aneel mantem taxa de retorno de Uruguaiana em 7,16%'. Reports ANEEL keeping the regulatory return for the Uruguaiana gas thermal plant at 7.16% (real, WACC-based, net of taxes) in the CVU calculation, over the generator's applied 10% rate. The CanalEnergia page returned a 403 proxy denial on direct WebFetch; wording confirmed via WebSearch result summary. Third-party source; regulator-set figure, not AES's own investment hurdle; AES/AES Brasil divested Uruguaiana in 2020.</t>
         </is>
       </c>
     </row>
@@ -9945,27 +9962,27 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Celsia</t>
+          <t>Enel Generación Chile</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>CELSIA CB</t>
+          <t>ENELGXCH CI</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>company-wide</t>
+          <t>renewables (standalone battery storage / BESS)</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>ROIC/ROCE target expressed as a spread over WACC</t>
+          <t>spread over WACC</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>&gt;200 bps above WACC (target ROCE = WACC + &gt;200 bps)</t>
+          <t>at least +300 bps above WACC (&gt;=300 basis points spread)</t>
         </is>
       </c>
       <c r="G9" s="26" t="inlineStr">
@@ -9975,17 +9992,17 @@
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>not stated (pre/post-tax and real/nominal not specified; ROCE/WACC in COP implied)</t>
+          <t>not stated (spread over the company's WACC; pre/post-tax and real/nominal not specified; currency not specified). This is storage/BESS-specific, explicitly NOT gas.</t>
         </is>
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t>Investor-relations page current as of 2025-2026 (objective reiterated in 2024 results and 2025 shareholder-assembly / EnergizarC communications)</t>
+          <t>Enel Chile Q1 2026 earnings call, late April 2026 (call/results reported ~29 Apr - 4 May 2026)</t>
         </is>
       </c>
       <c r="J9" s="25" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>earnings call transcript</t>
         </is>
       </c>
       <c r="K9" s="26" t="inlineStr">
@@ -9995,22 +10012,22 @@
       </c>
       <c r="L9" s="26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M9" s="25" t="inlineStr">
         <is>
-          <t>Celsia tiene como meta, en la búsqueda constante de maximizar el ROCE (retorno sobre el capital invertido), estar por encima de 200 puntos básicos del WACC (costo promedio ponderado del capital). / EN: Celsia's goal, in its constant pursuit of maximizing ROCE (return on invested capital), is to be more than 200 basis points above the WACC (weighted average cost of capital).</t>
+          <t>As reported consistently across transcripts of the official call: management stated the company advances standalone BESS projects only when returns are "at least 300 basis points above our WACC," and stress-tests them against more critical/stressed market scenarios. (Related: standalone BESS can be profitable, with higher profitability when the BESS is used to hybridize an existing power plant.) Exact primary-webcast wording could not be independently read due to proxy egress blocking (403).</t>
         </is>
       </c>
       <c r="N9" s="27" t="inlineStr">
         <is>
-          <t>https://www.celsia.com/es/inversionistas/celsia/por-que-invertir-en-celsia/</t>
+          <t>https://www.insidermonkey.com/blog/enel-chile-s-a-nyseenic-q1-2026-earnings-call-transcript-1753951/</t>
         </is>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t>Celsia investor-relations page '¿Por qué invertir en Celsia?'. Verbatim quote confirmed via WebSearch snippet of this exact official URL; direct WebFetch/curl blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com), so page/section could not be cited from the rendered document.</t>
+          <t>Enel Chile S.A. (NYSE:ENIC; intermediate parent of the listed entity Enel Generacion Chile) Q1 2026 earnings call, management remarks on standalone battery storage (BESS) capital allocation. Stated at the Enel Chile parent level, not at the listed entity Enel Generacion Chile. Verbatim wording corroborated identically across multiple independent transcript aggregators (Insider Monkey, Investing.com, Yahoo Finance highlights, AlphaSpread, Benzinga). The originally cited Seeking Alpha URL (article/4897916) could not be located in searches and is replaced here with a corroborated transcript page. All transcript pages and the official Enel Chile webcast return 403 at the agent proxy gateway (CONNECT policy denial), so the primary webcast/official transcript was not directly read.</t>
         </is>
       </c>
     </row>
@@ -10022,27 +10039,27 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Celsia</t>
+          <t>Enel Generación Chile</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>CELSIA CB</t>
+          <t>ENELGXCH CI</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Energy Services segment ('Servicios de energía') — not company-wide</t>
+          <t>renewables (group Renewables business under Enel SpA plan)</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>ROIC minus WACC spread target (segment)</t>
+          <t>spread over WACC</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>&gt; 118 bps ROIC-WACC spread (target for the Energy Services / 'Servicios de energía' business)</t>
+          <t>~300 bps average IRR-WACC spread targeted for new (renewables) projects</t>
         </is>
       </c>
       <c r="G10" s="26" t="inlineStr">
@@ -10052,17 +10069,17 @@
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>not stated (average spread of project IRR over WACC; pre/post-tax and real/nominal not specified; group reports in EUR). Applies to the group Renewables business, not gas/thermal.</t>
         </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
-          <t>2024 results / 2025 shareholder assembly (EnergizarC value-creation program)</t>
+          <t>Capital Markets Day, 19-22 Nov 2024 (2025-2027 Strategic Plan)</t>
         </is>
       </c>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t>press release</t>
+          <t>investor presentation</t>
         </is>
       </c>
       <c r="K10" s="26" t="inlineStr">
@@ -10077,17 +10094,17 @@
       </c>
       <c r="M10" s="25" t="inlineStr">
         <is>
-          <t>Buscan la expansión del spread entre ROIC vs. WACC para que sea mayor a 118 puntos básicos en el negocio de Servicios de energía. / EN: They seek to expand the ROIC vs. WACC spread to be greater than 118 basis points in the Energy Services business.</t>
+          <t>As reported from Enel's official 2025-2027 Strategic Plan materials: the group Renewables business targets an approximately "300 bps average spread between IRR and WACC" for new projects (Enel Americas states the same ~300 bps average IRR-WACC spread for new generation projects). Exact slide text could not be independently read due to proxy egress blocking the enel.com PDF (403).</t>
         </is>
       </c>
       <c r="N10" s="27" t="inlineStr">
         <is>
-          <t>https://www.celsia.com/es/noticias/en-la-asamblea-celsia-profundizo-sobre-su-valor-fundamental-y-resalto-que-el-retorno-total-al-accionista-tsr-en-el-2024-fue-del-362/</t>
+          <t>https://www.enel.com/content/dam/enel-com/documenti/investitori/informazioni-finanziarie/2024/2025-2027-strategic-plan.pdf</t>
         </is>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>Celsia press release on the 2024 shareholder assembly / EnergizarC program; segment-level target for the 'Servicios de energía' (Energy Services) business. Confirmed via WebSearch snippet of this exact official URL; direct WebFetch blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com).</t>
+          <t>Enel SpA (ultimate controlling group) 2025-2027 Strategic Plan / Capital Markets Day presentation. CORRECTION vs draft: the ~300 bps average IRR-WACC spread is specifically the target for the group RENEWABLES business (mirrored in Enel Americas' 2025-2027 generation plan), NOT a blanket group-wide-across-all-businesses metric as the draft implied by labeling it 'group-level'. Stated at Enel SpA group level for the renewables/generation business, not at Enel Chile or Enel Generacion Chile. The official enel.com PDF and enelamericas.com annexes return 403 at the proxy gateway; the figure and its renewables attribution are corroborated across multiple independent summaries of the official plan.</t>
         </is>
       </c>
     </row>
@@ -10099,611 +10116,779 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
+          <t>Engie Brasil / ENGIE</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>EGIE3 BZ</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>group-level</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>spread over WACC (IRR minus WACC)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>IRR minus WACC spread of at least 150-250 bps (reference ~200 bps), accompanied by an NPV/Capex value-creation criterion of ~20-25%</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>Not stated precisely. ENGIE group applies technology- and contract-differentiated WACCs; the portfolio is designed to deliver group WACC + ~200 bps. Pre/post-tax, real vs nominal and currency not specified by the company. NOTE: this is a controlling-parent (ENGIE SA, Paris-listed) group framework, NOT a figure stated by the Brazilian listed entity Engie Brasil Energia (EGIE3).</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>Reiterated at ENGIE group H1 2025 results (1 August 2025); framework set out earlier at ENGIE Capital Markets Day / investor updates (2023-2025)</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>earnings call transcript / investor presentation (group-level, controlling parent ENGIE SA)</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>Corroborated across multiple WebSearch results of official ENGIE documents (primary PDF could not be opened in this environment due to an egress-policy 403): ENGIE requires investments to match or exceed an IRR minus WACC spread of at least 150 to 250 basis points (reference ~200 bps), together with an NPV/Capex ratio of roughly 20-25%. [English; corroborated by search snippets of the ENGIE H1 2025 transcript and fact sheets, but not a page-level verified verbatim quote]</t>
+        </is>
+      </c>
+      <c r="N11" s="27" t="inlineStr">
+        <is>
+          <t>https://www.engie.com/sites/default/files/assets/documents/2025-08/ENGIE%20H1%202025%20-%20Transcript.pdf</t>
+        </is>
+      </c>
+      <c r="O11" s="25" t="inlineStr">
+        <is>
+          <t>ENGIE SA (Paris-listed controlling parent) H1 2025 results transcript, capital-allocation/investment-discipline section. Canonical IR path (dated 2025-08) verified as a live official URL via WebSearch; an equivalent mirror exists at https://www.engie.com/app/uploads/2026/03/ENGIE-H1-2025-Transcript.pdf (the URL cited in the original draft). The 150-250 bps IRR-WACC spread plus ~20-25% NPV/Capex criterion is corroborated by multiple official ENGIE documents (H1 2025 transcript and fact sheets). GROUP LEVEL, not the Brazilian listed entity. Page-level verbatim could not be extracted (see verification_notes: WebFetch blocked by egress policy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Celsia</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>CELSIA CB</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>company-wide</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>ROIC/ROCE target expressed as a spread over WACC</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>&gt;200 bps above WACC (target ROCE = WACC + &gt;200 bps)</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>not stated (pre/post-tax and real/nominal not specified; ROCE/WACC in COP implied)</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>Investor-relations page current as of 2025-2026 (objective reiterated in 2024 results and 2025 shareholder-assembly / EnergizarC communications)</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>Celsia tiene como meta, en la búsqueda constante de maximizar el ROCE (retorno sobre el capital invertido), estar por encima de 200 puntos básicos del WACC (costo promedio ponderado del capital). / EN: Celsia's goal, in its constant pursuit of maximizing ROCE (return on invested capital), is to be more than 200 basis points above the WACC (weighted average cost of capital).</t>
+        </is>
+      </c>
+      <c r="N12" s="27" t="inlineStr">
+        <is>
+          <t>https://www.celsia.com/es/inversionistas/celsia/por-que-invertir-en-celsia/</t>
+        </is>
+      </c>
+      <c r="O12" s="25" t="inlineStr">
+        <is>
+          <t>Celsia investor-relations page '¿Por qué invertir en Celsia?'. Verbatim quote confirmed via WebSearch snippet of this exact official URL; direct WebFetch/curl blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com), so page/section could not be cited from the rendered document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Celsia</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>CELSIA CB</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Energy Services segment ('Servicios de energía') — not company-wide</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>ROIC minus WACC spread target (segment)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>&gt; 118 bps ROIC-WACC spread (target for the Energy Services / 'Servicios de energía' business)</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>2024 results / 2025 shareholder assembly (EnergizarC value-creation program)</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="inlineStr">
+        <is>
+          <t>press release</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>Buscan la expansión del spread entre ROIC vs. WACC para que sea mayor a 118 puntos básicos en el negocio de Servicios de energía. / EN: They seek to expand the ROIC vs. WACC spread to be greater than 118 basis points in the Energy Services business.</t>
+        </is>
+      </c>
+      <c r="N13" s="27" t="inlineStr">
+        <is>
+          <t>https://www.celsia.com/es/noticias/en-la-asamblea-celsia-profundizo-sobre-su-valor-fundamental-y-resalto-que-el-retorno-total-al-accionista-tsr-en-el-2024-fue-del-362/</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t>Celsia press release on the 2024 shareholder assembly / EnergizarC program; segment-level target for the 'Servicios de energía' (Energy Services) business. Confirmed via WebSearch snippet of this exact official URL; direct WebFetch blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>B · Investment hurdle (spread / target IRR)</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
           <t>AES Brasil / AES Corp</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>AESO3 BZ</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>group-level</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>target return range (unlevered contracted return / ROIC-type, i.e. project IRR)</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>12% to 15% (data-center PPAs at the 'higher end' of the range; management framed development toward the upper half)</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>Unlevered / contracted-return basis (multiple independent transcript summaries describe this as AES's '12%-15% unlevered returns guidance range' for renewable/PPA investments; analyst framed the question as 'contracted ROIC or unlevered returns'). Currency USD (parent group, AES Corporation). Real vs nominal: not stated. Pre-tax vs post-tax: not stated.</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>AES Corporation Q3 2025 earnings call, 5 November 2025</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t>earnings call transcript</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>Official</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M11" s="25" t="inlineStr">
+      <c r="M14" s="25" t="inlineStr">
         <is>
           <t>Corroborated across independent transcript summaries: on returns for recent data-center PPAs, 'The returns on these tend to be at the higher end of our 12% to 15% [range].' Characterized elsewhere as AES's '12%-15% unlevered returns guidance range' for renewable-energy investments/PPAs. English original. (Exact verbatim sentence not read from a primary page — all transcript hosts 403-blocked; wording reconstructed from multiple concordant search summaries.)</t>
         </is>
       </c>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>https://www.insidermonkey.com/blog/the-aes-corporation-nyseaes-q3-2025-earnings-call-transcript-1641160/</t>
         </is>
       </c>
-      <c r="O11" s="25" t="inlineStr">
+      <c r="O14" s="25" t="inlineStr">
         <is>
           <t>AES Corporation (parent) Q3 2025 earnings call, 5 Nov 2025 — Q&amp;A. Analyst Dimple Gosai (Bank of America) asked how the contracted ROIC / unlevered returns on recent data-center PPAs compared to the legacy book; CEO Andres Gluski answered that returns tend to be at the higher end of the 12%-15% range. Official event is the AES Q3 2025 earnings webcast (aes.com/investors). VERIFICATION: the cited insidermonkey URL and every alternate full-transcript host (theglobeandmail.com, fool.com, seekingalpha.com, investing.com, aol.com, finance.yahoo.com, alphaspread.com, tipranks.com) returned HTTP 403 proxy/policy denials on direct WebFetch, so wording could not be read from the primary page. The figure and framing were corroborated across three independent WebSearch result summaries.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>C · Stated / regulatory WACC benchmark</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Celsia</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>CELSIA CB</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>company-wide</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>WACC (stated actual) with ROCE</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>WACC 13.02%; ROCE 14.33% (positive differential of 131 bps), FY2022</t>
         </is>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>not stated (COP, nominal implied; pre/post-tax not specified)</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>FY2022 results (reported early 2023)</t>
         </is>
       </c>
-      <c r="J12" s="29" t="inlineStr">
+      <c r="J15" s="29" t="inlineStr">
         <is>
           <t>press release</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t>Official</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M12" s="29" t="inlineStr">
+      <c r="M15" s="29" t="inlineStr">
         <is>
           <t>Al cierre de 2022, y a pesar del fuerte incremento de las tasas de interés, Celsia mantuvo un diferencial positivo de 131 puntos básicos entre el ROCE de 14,33% frente a un WACC de 13,02%. / EN: At year-end 2022, and despite the sharp rise in interest rates, Celsia maintained a positive differential of 131 basis points between a ROCE of 14.33% and a WACC of 13.02%.</t>
         </is>
       </c>
-      <c r="N12" s="31" t="inlineStr">
+      <c r="N15" s="31" t="inlineStr">
         <is>
           <t>https://www.celsia.com/es/noticias/resultados-de-celsia-en-2022/</t>
         </is>
       </c>
-      <c r="O12" s="29" t="inlineStr">
+      <c r="O15" s="29" t="inlineStr">
         <is>
           <t>Celsia FY2022 results press release ('Resultados de Celsia en 2022'). Figures (ROCE 14.33% vs WACC 13.02%, +131 bps) confirmed via WebSearch snippet of this exact official URL; direct WebFetch blocked by organization egress policy (proxy CONNECT 403 on www.celsia.com).</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>C · Stated / regulatory WACC benchmark</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>AXIA (ex-Eletrobras)</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>AXIA3 BZ</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>transmission</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>regulated (RAB) WACC</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>7.89% real, after taxes (2025 ANEEL transmission/generation regulatory cycle); ~12.12% pre-tax real (i.e., IPCA + ~12.12%)</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr">
         <is>
           <t>post-tax AND real (regulatory WACC as defined by ANEEL); currency BRL; applied over an IPCA-indexed regulatory remuneration base (RAB), so effectively IPCA + ~12.12% on a pre-tax basis. Now confirmed as a REAL after-tax rate (the draft had left real/nominal ambiguous).</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>ANEEL 2025 tariff cycle (rate in effect from 1 March 2025; superseded by 8.00% from 1 March 2026 per ANEEL's March 2026 WACC update)</t>
         </is>
       </c>
-      <c r="J13" s="29" t="inlineStr">
+      <c r="J16" s="29" t="inlineStr">
         <is>
           <t>regulatory filing</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>Third-party</t>
         </is>
       </c>
-      <c r="L13" s="30" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M13" s="29" t="inlineStr">
+      <c r="M16" s="29" t="inlineStr">
         <is>
           <t>PT (paraphrase of ANEEL communication, via poder360/cenarioenergia): 'A taxa regulatoria real apos impostos foi definida em 8,10% para o segmento de distribuicao e 8,00% para transmissao e geracao. Antes dos impostos, os percentuais chegam a 12,28% e 12,11%, respectivamente. Em relacao ao ciclo anterior, houve aumento de 0,07 ponto percentual no WACC aplicado a distribuicao e de 0,11 ponto percentual para transmissao e geracao.' EN: 'The real after-tax regulatory rate was set at 8.10% for distribution and 8.00% for transmission and generation. Pre-tax, the percentages reach 12.28% and 12.11% respectively. Versus the previous cycle, there was an increase of 0.07pp for distribution and 0.11pp for transmission and generation.' [Implies prior/2025 transmission WACC = 8.00% - 0.11pp = 7.89% real after-tax.] Note: I could not open ANEEL's page directly (HTTP 403 via WebFetch); text is from WebSearch summaries of the official ANEEL release and Brazilian energy press.</t>
         </is>
       </c>
-      <c r="N13" s="31" t="inlineStr">
+      <c r="N16" s="31" t="inlineStr">
         <is>
           <t>https://www.gov.br/aneel/pt-br/assuntos/noticias/2026/aneel-atualiza-taxa-regulatoria-de-remuneracao-do-capital-wacc-regulatorio</t>
         </is>
       </c>
-      <c r="O13" s="29" t="inlineStr">
+      <c r="O16" s="29" t="inlineStr">
         <is>
           <t>Official ANEEL (Brazilian electricity regulator) communication on the regulatory WACC. The March 2026 update sets transmission/generation regulatory WACC at 8.00% real after-tax (12.11% pre-tax), described as a +0.11 percentage-point increase over the prior (2025) cycle, which therefore was 7.89% real after-tax. Sector-wide value applying to all Brazilian transmission concessionaires including AXIA/Eletrobras transmission and Law 12.783/13 quota-regime assets. Corroborated by poder360.com.br and cenarioenergia.com.br coverage. NOTE: this is a sector-wide REGULATORY WACC set by the regulator, not an internal investment hurdle chosen by the company; included as the benchmark ANEEL WACC that AXIA's own materials reference (AXIA Q4 2025 investor slides describe its regulated transmission WACC as 'IPCA + 12.12%').</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>C · Stated / regulatory WACC benchmark</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>AXIA (ex-Eletrobras)</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>AXIA3 BZ</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>transmission</t>
         </is>
       </c>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>regulated (RAB) return / WACC</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>ANEEL-defined regulatory WACC for Law 12.783/13 assets (transmission, quota-regime hydro, Eletronuclear); no company-specific percentage stated in the Eletrobras SEC disclosure itself</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>ANEEL regulatory WACC (real, after taxes per ANEEL methodology); the Eletrobras SEC filing text located did not itself restate pre/post-tax, real/nominal, or currency. Methodology set by ANEEL Resolution 874/2020 (WACC methodology) / REN 918/2021 (calculation procedure for Law 12.783/13 concessions).</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>recurring disclosure in Eletrobras SEC filings (Form 20-F and quarterly 6-K market-letter annexes, 2021-2022)</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="J17" s="29" t="inlineStr">
         <is>
           <t>regulatory filing</t>
         </is>
       </c>
-      <c r="K14" s="30" t="inlineStr">
+      <c r="K17" s="30" t="inlineStr">
         <is>
           <t>Official</t>
         </is>
       </c>
-      <c r="L14" s="30" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M14" s="29" t="inlineStr">
+      <c r="M17" s="29" t="inlineStr">
         <is>
           <t>Reconstructed (NOT independently verified at the SEC page, which returned 403): 'Compensation for transmission concessions is determined through WACC, the weighted average cost of capital, defined by ANEEL... Resolution No. 874/2020 established the WACC to be applied to the investment for (i) transmission assets, hydroelectric plants subject to the physical guarantee and power quota regime (Law No. 12,783/13), and (ii) Eletronuclear.'</t>
         </is>
       </c>
-      <c r="N14" s="31" t="inlineStr">
+      <c r="N17" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1439124/000129281421001692/ebr20210422_6k.htm</t>
         </is>
       </c>
-      <c r="O14" s="29" t="inlineStr">
+      <c r="O17" s="29" t="inlineStr">
         <is>
           <t>Eletrobras Form 6-K market-letter annex / Form 20-F, transmission concession compensation and regulatory framework section. COULD NOT be opened for page-level verification: SEC.gov returned HTTP 403 to WebFetch on every attempt. The substance is corroborated: ANEEL Resolution 874/2020 approving the updated WACC methodology (2020) and REN 918/2021 defining WACC for Law 12.783/13 transmission and quota-regime generation (incl. Eletronuclear) are confirmed via ANEEL/press sources. This is a regulator-set RAB WACC, not an internal company hurdle, and no specific percentage appears in the company disclosure located.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>D · Third-party estimate (not company-stated)</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Engie Brasil / ENGIE</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>EGIE3 BZ</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>transmission</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>IRR (real, project-level, third-party estimate)</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>~7-8% real IRR estimated for ENGIE's winning lots in ANEEL Transmission Auction 01/2026 (analyst estimate); described by analysts as modest / below the sector historical average</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>Real; project/asset-level IRR; pre/post-tax not stated; BRL. This is an analyst-estimated achieved return on new regulated (transmission) capex, NOT a company-stated hurdle. Deságio médio (average discount) on the lots reported at ~53%.</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>March 2026 (post-auction analyst commentary)</t>
         </is>
       </c>
-      <c r="J15" s="33" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>third-party analyst/press (Guia do Investidor; also InfoMoney, Acionista, ADVFN)</t>
         </is>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K18" s="34" t="inlineStr">
         <is>
           <t>Third-party</t>
         </is>
       </c>
-      <c r="L15" s="34" t="inlineStr">
+      <c r="L18" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M15" s="33" t="inlineStr">
+      <c r="M18" s="33" t="inlineStr">
         <is>
           <t>Per analyst commentary summarized in Brazilian press (WebSearch): 'os projetos podem entregar TIR real entre 7% e 8%, o que e considerado modesto para o setor' / 'the projects may deliver a real IRR between 7% and 8%, considered modest for the sector'. [Portuguese source with English translation; third-party, paraphrased/snippet-level, not page-level verbatim]</t>
         </is>
       </c>
-      <c r="N15" s="35" t="inlineStr">
+      <c r="N18" s="35" t="inlineStr">
         <is>
           <t>https://guiadoinvestidor.com.br/mercado/engie-egie3-leva-leilao-da-aneel-mas-retorno-decepciona-e-acende-alerta-no-mercado/</t>
         </is>
       </c>
-      <c r="O15" s="33" t="inlineStr">
+      <c r="O18" s="33" t="inlineStr">
         <is>
           <t>Brazilian financial press reporting analyst estimates of real IRR on ENGIE's 2026 transmission auction lots (lot 2 and sub-lots 3A-3D via ENGIE Transmissao de Energia Participacoes, ~R$1.6bn capex, RAP ~R$122.7m). Third-party, not company-disclosed. Included only as a directional benchmark of the returns ENGIE is accepting on new regulated transmission capex. Article confirmed live via WebSearch (page body could not be opened via WebFetch due to egress-policy 403).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>D · Third-party estimate (not company-stated)</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Grupo Energía Bogotá</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>GEB CB</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>group-level</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>sell-side analyst valuation WACC for GEB business units (third-party, NOT company-stated)</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>~10.3% (attributed to 2024 valuation, UNVERIFIED); ~11.3% average for 2023 (corroborated), with ~10.4% for Enel Colombia</t>
         </is>
       </c>
-      <c r="G16" s="34" t="inlineStr">
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>not stated (Beta 0.55x for energy companies; gas-distribution beta reported as 0.83x for the 2023 exercise — draft's '0.7x' could not be corroborated)</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>Davivienda Corredores 'Zoom a las Empresas – GEB' (2023 edition corroborated; 2024 edition figure of ~10.3% not independently verifiable)</t>
         </is>
       </c>
-      <c r="J16" s="33" t="inlineStr">
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>investor presentation</t>
         </is>
       </c>
-      <c r="K16" s="34" t="inlineStr">
+      <c r="K19" s="34" t="inlineStr">
         <is>
           <t>Third-party</t>
         </is>
       </c>
-      <c r="L16" s="34" t="inlineStr">
+      <c r="L19" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M16" s="33" t="inlineStr">
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>"...un WACC promedio de 11.3% para las unidades de TGI, Cálidda, Dunas, Transmisión y Gebbras, dejando con un WACC de 10.4% a Enel Colombia" with "...una Beta (u) de 0.55x para compañías de energía y 0.83x para compañías de distribución de gas" ("...an average WACC of 11.3% for the TGI, Cálidda, Dunas, Transmisión and Gebbras units, leaving Enel Colombia with a WACC of 10.4%"; Beta of 0.55x for energy companies and 0.83x for gas-distribution companies). Paraphrased from Davivienda Corredores 'Zoom a las Empresas – GEB'; exact page text not directly retrievable (HTTP 403). The ~10.3%/2024 figure in the draft was not corroborated.</t>
         </is>
       </c>
-      <c r="N16" s="35" t="inlineStr">
+      <c r="N19" s="35" t="inlineStr">
         <is>
           <t>https://libro.daviviendacorredores.com/2023/zoom-a-empresas/geb/</t>
         </is>
       </c>
-      <c r="O16" s="33" t="inlineStr">
+      <c r="O19" s="33" t="inlineStr">
         <is>
           <t>THIRD-PARTY / SELL-SIDE ANALYST report (Davivienda Corredores), not a GEB official disclosure. Corroborated figures (via search summaries; direct fetch 403): an ~11.3% average WACC applied to TGI, Cálidda, Dunas, Transmisión and Gebbras, and ~10.4% for Enel Colombia, with a Beta of 0.55x for energy companies and 0.83x for gas-distribution companies — these appear in the 2023 exercise. The draft's specific claim of ~10.3% for 2024 (down from 11.3%) and a 0.7x gas-distribution beta could NOT be independently corroborated; both the 2023 and 2024 Davivienda pages returned HTTP 403. This is an analyst's valuation WACC, not confirmed verbatim from GEB's own Reporte Integrado or estados financieros (GEB official pages also 403).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>D · Third-party estimate (not company-stated)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Empresa Eléctrica Pehuenche</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>PEHUEN CI</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>group-level</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>WACC (third-party computed, ultimate-parent level)</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>~8.0-8.8% (post-tax, nominal, USD; analyst-computed)</t>
         </is>
       </c>
-      <c r="G17" s="34" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H17" s="33" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>post-tax, nominal; USD; analyst-computed (not stated by the company)</t>
         </is>
       </c>
-      <c r="I17" s="33" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>as of 2026 (third-party data services)</t>
         </is>
       </c>
-      <c r="J17" s="33" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="K20" s="34" t="inlineStr">
         <is>
           <t>Third-party</t>
         </is>
       </c>
-      <c r="L17" s="34" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M17" s="33" t="inlineStr">
+      <c r="M20" s="33" t="inlineStr">
         <is>
           <t>GuruFocus: 'Enel Chile WACC %: 8.8%'. AlphaSpread: 'Enel Chile's current Cost of Equity is 8.85%, while its WACC stands at 8.08%; cost of debt is 6.84%.' [Third-party analyst-computed WACC, not a company-stated hurdle rate; grandparent/group level, not gas-specific.]</t>
         </is>
       </c>
-      <c r="N17" s="35" t="inlineStr">
+      <c r="N20" s="35" t="inlineStr">
         <is>
           <t>https://www.gurufocus.com/term/wacc/NYSE:ENIC/WACC-/Enel-Chile</t>
         </is>
       </c>
-      <c r="O17" s="33" t="inlineStr">
+      <c r="O20" s="33" t="inlineStr">
         <is>
           <t>GuruFocus / AlphaSpread WACC pages for Enel Chile SA (ENIC), the ultimate listed parent of Pehuenche via Enel Generacion Chile. GuruFocus: WACC 8.8%; AlphaSpread: WACC ~8.08%, cost of equity ~8.85%, cost of debt ~6.84%, debt weight ~38%. This is a computed figure, NOT a company-disclosed hurdle rate.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>A · Gas-specific — a rate explicitly tied to gas-fired generation or gas infrastructure.</t>
-        </is>
-      </c>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="37" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>B · Investment hurdle — a target IRR or minimum spread over WACC the company applies to investments/PPAs (mostly renewables/portfolio-wide; none gas-specific).</t>
-        </is>
-      </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
-      <c r="K21" s="36" t="n"/>
-      <c r="L21" s="36" t="n"/>
-      <c r="M21" s="36" t="n"/>
-      <c r="N21" s="36" t="n"/>
-      <c r="O21" s="37" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>C · Stated / regulatory WACC — a company-stated actual WACC, or the regulator-set (RAB) WACC the company earns on regulated assets.</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="36" t="n"/>
-      <c r="O22" s="37" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>D · Third-party estimate — analyst / data-vendor computed figures; NOT company-stated. Included only as directional context.</t>
+          <t>A · Gas-specific — a rate explicitly tied to gas-fired generation or gas infrastructure.</t>
         </is>
       </c>
       <c r="B23" s="36" t="n"/>
@@ -10724,7 +10909,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>'Official?' = Official means from the company or its controlling parent/group; the regulatory-WACC rows are set by the regulator (ANEEL/CREG), noted in Source detail.</t>
+          <t>B · Investment hurdle — a target IRR or minimum spread over WACC the company applies to investments/PPAs (mostly renewables/portfolio-wide unless noted).</t>
         </is>
       </c>
       <c r="B24" s="36" t="n"/>
@@ -10742,15 +10927,78 @@
       <c r="N24" s="36" t="n"/>
       <c r="O24" s="37" t="n"/>
     </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>C · Stated / regulatory WACC — a company-stated actual WACC, or the regulator-set (RAB) WACC the company earns on regulated assets.</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="36" t="n"/>
+      <c r="N25" s="36" t="n"/>
+      <c r="O25" s="37" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>D · Third-party estimate — analyst / data-vendor computed figures; NOT company-stated. Directional context only.</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="36" t="n"/>
+      <c r="O26" s="37" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>'Official?' = from the company or its controlling parent/group; the regulatory-WACC rows are set by the regulator (ANEEL/CREG), noted in Source detail. Eneva IRR %s are read off a chart (approximate).</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="36" t="n"/>
+      <c r="N27" s="36" t="n"/>
+      <c r="O27" s="37" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A26:O26"/>
     <mergeCell ref="A24:O24"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="A27:O27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId1"/>
@@ -10767,12 +11015,562 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Eneva (ENEV3 BZ) — project-level real IRRs, from Corporate Presentation April 2026, slide 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source: Eneva Corporate Presentation, April 2026, slide 13 ('…With Capital Allocations with Sound Returns…'), provided by user (official deck; api.mziq.com blocked in-environment). Metric = real IRR (leveraged unless noted). IRR values are APPROXIMATE — read off the chart against the 0–30% axis; the deck prints no numeric IRR table. Project leverage (% of capex) and average debt cost (IPCA+) ARE printed on the slide. Returns are presented as a spread over the NTN-b 2040 (IPCA-linked Treasury = real risk-free rate, ~6–9% real over the period). Official IR location: https://ri.eneva.com.br/en/financial-information/presentations-and-conference-calls/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>https://ri.eneva.com.br/en/financial-information/presentations-and-conference-calls/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Vintage</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Real IRR (approx.)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Project leverage (% capex)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Avg debt cost</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>IRR basis</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Parnaíba V</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Dec-18</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>~20%</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>IPCA + 3.1%</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Gas-to-power thermal; Capex R$1.5bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Azulão-Jaguatirica (greenfield)</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>~11%</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>IPCA + 3.3%</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>G2P greenfield (isolated system); Capex R$2.2bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Parnaíba VI</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Dec-19</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>~14%</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>IPCA + 4.4%</t>
+        </is>
+      </c>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Gas thermal; Capex R$0.8bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Focus (Futura) acquisition</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Dec-21</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>~10-11%</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>IPCA + 5.8%</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t>Incl. Futura 1 solar + trading cos; Capex R$3.0bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Small-Scale LNG (greenfield)</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>~24-30%</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>IPCA + 3.4%</t>
+        </is>
+      </c>
+      <c r="F9" s="41" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Greenfield LNG; Capex R$1.0bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Fortaleza TPP (Termofortaleza)</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Jun-22</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>~20%</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>Unleveraged at acq.</t>
+        </is>
+      </c>
+      <c r="G10" s="39" t="inlineStr">
+        <is>
+          <t>Gas thermal; Investment R$0.5bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Azulão 950 (greenfield)</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>~16-17%</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>on going</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>IPCA + 4.1%</t>
+        </is>
+      </c>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>G2P greenfield; est. Capex R$5.8bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>Celse acquisition</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>Dec-22</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>~16%</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>IPCA + 7.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
+        <is>
+          <t>Sergipe gas thermal (Celse); Investment R$6.1bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>BTG assets</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Nov-24</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t>~20-24%</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>IPCA + 6.9%</t>
+        </is>
+      </c>
+      <c r="F13" s="41" t="inlineStr">
+        <is>
+          <t>Leveraged</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Investment R$3.1bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>LRCAP26 - Sergipe Hub</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>~26-27%</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>2026 Capacity Auction new G2P; part of R$18.2bn capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>LRCAP26 - Ceará Hub</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t>~22%</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>2026 Capacity Auction new G2P</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>LRCAP26 - Southeast Hub</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>~14%</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="G16" s="39" t="inlineStr">
+        <is>
+          <t>2026 Capacity Auction new G2P</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>LRCAP26 = Brazil's 2026 Capacity Reserve Auction; those three hubs are NEW gas-to-power projects shown at UNLEVERED real IRR (highlighted). All other rows are leveraged real IRRs (Fortaleza TPP unleveraged at acquisition).</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="37" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10828,39 +11626,39 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="96" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="100" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>ENEV3 BZ</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Eneva</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>BLOCKED — likely has data</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Brazil's gas-to-power pure-play; the single most likely to disclose a gas IRR. Third parties reference an 'Unlevered IRR of Projects' slide in Eneva's corporate presentation showing per-project unlevered IRRs (Azulão-Jaguatirica, Parnaíba V). XP research characterises Eneva's realised returns as &gt;20% real IRR since 2017 (a track record, not a stated hurdle).</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>api.mziq.com; ri.eneva.com.br; rad.cvm.gov.br; earnings-call transcript hosts</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>The current Eneva corporate presentation 'Unlevered IRR of Projects' slide; Formulário de Referência; and the DFP/ITR impairment notes (value-in-use 'taxa de desconto'/WACC for the thermal &amp; E&amp;P units) — the most likely official WACC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="96" customHeight="1">
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>FOUND (Apr-2026 deck)</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>RESOLVED using the deck you provided. Eneva discloses per-project REAL IRRs (slide 13): NEW 2026-auction gas hubs at ~14–27% unlevered; existing G2P/thermal/LNG at ~10–30% leveraged. Framed as a spread over NTN-b 2040 (real risk-free). See findings tab + 'Eneva Project IRRs' tab.</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>api.mziq.com; ri.eneva.com.br (still blocked in-env — data now sourced from the uploaded deck)</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>For exact IRR %s (deck shows a chart, not a table): the impairment/value-in-use 'taxa de desconto' in the DFP/ITR notes, and any per-project figures in the Formulário de Referência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="38" t="inlineStr">
         <is>
           <t>COLBUN CI</t>
@@ -10878,7 +11676,7 @@
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
-          <t>Disclosure is framed around CapEx guidance and project pipeline, not explicit return thresholds. Management stated BESS projects are always linked to a PPA (i.e. not merit-order/spread bets). No target IRR/WACC/spread found in search snippets.</t>
+          <t>Disclosure framed around CapEx guidance and project pipeline, not explicit return thresholds. Management stated BESS projects are always linked to a PPA. No target IRR/WACC/spread found in search snippets.</t>
         </is>
       </c>
       <c r="E4" s="39" t="inlineStr">
@@ -10892,7 +11690,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="96" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>AURE3 BZ</t>
@@ -10910,7 +11708,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>3rd-largest Brazilian generator, 100% renewable (hydro + wind/solar) + trading, ~no gas — so no gas/thermal hurdle exists. No company-stated hurdle/target IRR/WACC found; all WACC/IRR figures located were third-party.</t>
+          <t>3rd-largest Brazilian generator, 100% renewable + trading, ~no gas — so no gas/thermal hurdle exists. No company-stated hurdle/target IRR/WACC found; all located figures were third-party.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -10920,11 +11718,11 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Audited financial statements: impairment / value-in-use discount rate (the most likely place a company discount rate is disclosed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="96" customHeight="1">
+          <t>Audited financial statements: impairment / value-in-use discount rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="38" t="inlineStr">
         <is>
           <t>ENLASA CI</t>
@@ -10942,7 +11740,7 @@
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>Small backup/peaking diesel-&amp;-gas generator; does not publish investor-day-style return frameworks. Only bond-line mechanics and rating narrative surfaced (Category AA; EBITDA floor ~US$10m).</t>
+          <t>Small backup/peaking diesel-&amp;-gas generator; does not publish investor-day-style return frameworks. Only bond-line mechanics and rating narrative surfaced.</t>
         </is>
       </c>
       <c r="E6" s="39" t="inlineStr">
@@ -10956,7 +11754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="96" customHeight="1">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>EGIE3 BZ</t>
@@ -10974,7 +11772,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>The listed Brazilian entity does not state its own hurdle; the ENGIE group applies an IRR-minus-WACC spread of ~150–250 bps plus an NPV/Capex value-creation test. Captured on the findings tab.</t>
+          <t>Listed BR entity states no own hurdle; ENGIE group applies IRR-minus-WACC spread of ~150–250 bps + an NPV/Capex value-creation test. On findings tab.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -10984,11 +11782,11 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>ENGIE group H1/FY results transcripts &amp; fact sheets; Engie Brasil Formulário de Referência for any local WACC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="96" customHeight="1">
+          <t>ENGIE group H1/FY transcripts &amp; fact sheets; Engie Brasil Formulário de Referência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
       <c r="A8" s="38" t="inlineStr">
         <is>
           <t>ENELGXCH CI</t>
@@ -11006,21 +11804,21 @@
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>Hurdle stated at Enel Chile / Enel group level (≥300 bps above WACC for BESS; ~300 bps IRR-WACC for renewables). Renewables/storage-specific, explicitly not gas. Captured on the findings tab.</t>
+          <t>Hurdle at Enel Chile / Enel group level (≥300 bps above WACC for BESS; ~300 bps IRR-WACC for renewables). Renewables/storage-specific, not gas. On findings tab.</t>
         </is>
       </c>
       <c r="E8" s="39" t="inlineStr">
         <is>
-          <t>enel.com; enelamericas.com; transcript hosts (verbatim blocked)</t>
+          <t>enel.com; enelamericas.com; transcript hosts</t>
         </is>
       </c>
       <c r="F8" s="39" t="inlineStr">
         <is>
-          <t>Enel Chile Q1 2026 call transcript; Enel 2025–2027 Strategic Plan deck for the exact renewables IRR-WACC slide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="96" customHeight="1">
+          <t>Enel Chile Q1-26 call transcript; Enel 2025–27 Strategic Plan deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CELSIA CB</t>
@@ -11038,21 +11836,21 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Company-wide ROCE target &gt;200 bps above WACC; actual FY2022 WACC 13.02% / ROCE 14.33%. Not gas-specific though Celsia owns gas thermal. Captured on the findings tab.</t>
+          <t>Company-wide ROCE target &gt;200 bps above WACC; actual FY22 WACC 13.02% / ROCE 14.33%. Not gas-specific though Celsia owns gas thermal. On findings tab.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>www.celsia.com (verbatim blocked; quotes from search snippets)</t>
+          <t>www.celsia.com (verbatim blocked; quotes from snippets)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>'¿Por qué invertir en Celsia?' IR page; Informe Integrado; results releases — for the current ROCE/WACC figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="96" customHeight="1">
+          <t>'¿Por qué invertir en Celsia?' IR page; Informe Integrado; results releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" s="38" t="inlineStr">
         <is>
           <t>GEB CB</t>
@@ -11070,21 +11868,21 @@
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
-          <t>Gas-transport regulated WACC 11.88% (pre-tax, real, constant COP), set by CREG for TGI — a genuine gas-infrastructure return, though regulator-set, not GEB's own hurdle. Rolled back / refund ordered by CREG in Mar-2026. Captured on the findings tab.</t>
+          <t>Gas-transport regulated WACC 11.88% (pre-tax, real, constant COP), set by CREG for TGI — a real gas-infrastructure return, regulator-set. Rolled back/refund ordered Mar-26. On findings tab.</t>
         </is>
       </c>
       <c r="E10" s="39" t="inlineStr">
         <is>
-          <t>creg.gov.co; gestornormativo.creg.gov.co; GEB IR pages</t>
+          <t>creg.gov.co; GEB IR pages</t>
         </is>
       </c>
       <c r="F10" s="39" t="inlineStr">
         <is>
-          <t>Primary CREG Resolución 102 002 de 2023 &amp; Res. 103 de 2021; GEB Reporte Integrado for any group investment return criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="96" customHeight="1">
+          <t>Primary CREG Res. 102 002/2023 &amp; Res. 103/2021; GEB Reporte Integrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>AXIA3 BZ</t>
@@ -11102,21 +11900,21 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>No internal hurdle found; sells mostly hydro. Its regulated transmission earns the ANEEL WACC ~7.89% real after-tax (2025; 8.00% from Mar-2026); AXIA slides describe it as 'IPCA + 12.12%'. Captured on the findings tab.</t>
+          <t>No internal hurdle found; mostly hydro. Regulated transmission earns ANEEL WACC ~7.89% real after-tax (2025; 8.00% from Mar-26); AXIA slides say 'IPCA + 12.12%'. On findings tab.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>sec.gov (20-F/6-K); aneel.gov.br pages (verbatim blocked)</t>
+          <t>sec.gov (20-F/6-K); aneel.gov.br</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>AXIA Business/Strategic Plan and Q4 2025 investor slides for any project return target; ANEEL WACC releases for the exact regulatory rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="96" customHeight="1">
+          <t>AXIA Business/Strategic Plan &amp; Q4-25 investor slides; ANEEL WACC releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100" customHeight="1">
       <c r="A12" s="38" t="inlineStr">
         <is>
           <t>AESO3 BZ</t>
@@ -11134,21 +11932,21 @@
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>AES (parent) targets 12–15% unlevered returns on renewable/PPA investments (data-center PPAs at the higher end). The one gas-specific figure (Uruguaiana 7.16% regulatory return) is ANEEL-set and the plant was divested in 2020. Captured on the findings tab.</t>
+          <t>AES (parent) targets 12–15% unlevered on renewable/PPA investments (data-center PPAs at higher end). One gas figure (Uruguaiana 7.16%) is ANEEL-set &amp; divested in 2020. On findings tab.</t>
         </is>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
-          <t>aes.com; transcript hosts (verbatim blocked)</t>
+          <t>aes.com; transcript hosts</t>
         </is>
       </c>
       <c r="F12" s="39" t="inlineStr">
         <is>
-          <t>AES Corp Q3 2025 call transcript; AES Brasil reference form. Note gas thermal was largely divested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="96" customHeight="1">
+          <t>AES Corp Q3-25 call transcript; AES Brasil reference form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="100" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>PEHUEN CI</t>
@@ -11166,7 +11964,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Hydro subsidiary of Enel Generación Chile; no own disclosure. Only third-party WACC for the ultimate parent Enel Chile (~8.0–8.8%) exists. No gas.</t>
+          <t>Hydro subsidiary of Enel Generación Chile; no own disclosure. Only third-party WACC for parent Enel Chile (~8.0–8.8%). No gas.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -11180,7 +11978,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="96" customHeight="1">
+    <row r="14" ht="100" customHeight="1">
       <c r="A14" s="38" t="inlineStr">
         <is>
           <t>ENMT4 BZ</t>
@@ -11198,21 +11996,21 @@
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>Electricity distribution utility, not a generator. Its regulated return is the ANEEL distribution WACC (~8.10% real after-tax, 2026). No generation/gas hurdle.</t>
+          <t>Electricity distribution utility, not a generator. Regulated by ANEEL distribution WACC (~8.10% real after-tax, 2026). No generation/gas hurdle.</t>
         </is>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
-          <t>energisa.com.br / api.mziq (not pursued — N/A)</t>
+          <t>energisa.com.br / api.mziq (N/A)</t>
         </is>
       </c>
       <c r="F14" s="39" t="inlineStr">
         <is>
-          <t>ANEEL distribution WACC releases if the regulated return is of interest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="96" customHeight="1">
+          <t>ANEEL distribution WACC releases if of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="100" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>EQMA3B BZ</t>
@@ -11230,21 +12028,21 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Electricity distribution utility, not a generator. Regulated by the ANEEL distribution WACC. No generation/gas hurdle.</t>
+          <t>Electricity distribution utility, not a generator. Regulated by ANEEL distribution WACC. No generation/gas hurdle.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>equatorialenergia.com.br (not pursued — N/A)</t>
+          <t>equatorialenergia.com.br (N/A)</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Equatorial group investor materials for any group project hurdle (not gas).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="96" customHeight="1">
+          <t>Equatorial group investor materials (not gas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
       <c r="A16" s="38" t="inlineStr">
         <is>
           <t>GEPA4 BZ</t>
@@ -11272,11 +12070,11 @@
       </c>
       <c r="F16" s="39" t="inlineStr">
         <is>
-          <t>Reference form / results, if any group return target exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="96" customHeight="1">
+          <t>Reference form / results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>PRMN3B BZ</t>
@@ -11308,7 +12106,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="96" customHeight="1">
+    <row r="18" ht="100" customHeight="1">
       <c r="A18" s="38" t="inlineStr">
         <is>
           <t>CEBR5 BZ</t>
@@ -11340,7 +12138,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="96" customHeight="1">
+    <row r="19" ht="100" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>PUNTILLA CI</t>
@@ -11372,7 +12170,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="96" customHeight="1">
+    <row r="20" ht="100" customHeight="1">
       <c r="A20" s="38" t="inlineStr">
         <is>
           <t>WIG JA</t>

--- a/LatAm_Power_Companies_Research.xlsx
+++ b/LatAm_Power_Companies_Research.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Gas &amp; Investment Hurdle Rates" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Eneva Project IRRs" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Hurdle Rates - Coverage &amp; Gaps" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Capacity IRR Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Capacity IRR - Synthesis" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +88,31 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +152,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5A88"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -330,6 +370,90 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,6 +965,2730 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Capacity-contract / availability-based generation — IRR &amp; discount-rate benchmarks (subject asset: operating, ~97% capacity revenue, Trinidad &amp; Tobago)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="86" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BASIS VARIES BY ROW — do not difference figures without converting. Columns flag levered/unlevered, real/nominal, pre/post-tax, currency. Merchant new-build (US CONE, NRG, ERCOT) is the CEILING, not your asset. Regulated returns (FERC ROE, ANEEL, Ofgem cap-floor) are the FLOOR. LatAm statutory capacity rates are REAL — add ~3-5% inflation for nominal. See the 'Capacity IRR - Synthesis' tab for the harmonised recommendation. Research note: many official PDFs were 403-blocked by this environment's egress policy; figures were captured via web-search of the official documents (links are canonical) and should be verified at source before use in a model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Source / mechanism</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Asset / context</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Contract-life stage</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Return metric &amp; value</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Lev / Unlev</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Real / Nom</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Ccy</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Off / 3P</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>TRINIDAD &amp; TOBAGO — the direct comps (IPP availability PPAs with T&amp;TEC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>Trinidad Generation Unlimited (TGU) — senior USD notes (Cbonds)</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>720 MW CCGT, 30-yr availability PPA to ~2041</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>Operating, mid-life</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t>~8.1% yield (7.75% coupon), US$525m due 2033</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="F5" s="49" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H5" s="49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>https://cbonds.com/bonds/1868901/</t>
+        </is>
+      </c>
+      <c r="L5" s="48" t="inlineStr">
+        <is>
+          <t>Actual local cost of SENIOR DEBT for a fully-contracted T&amp;T CCGT; embeds T&amp;TEC offtaker + Ba2 sovereign risk. Debt, not equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>Energy for Growth Hub — T&amp;T PPA review</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>T&amp;TEC single-buyer PPAs (PowerGen, TGU, Trinity, Lightsource)</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>All stages</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>Capacity charge covers fixed cost, debt service + 'an agreed equity return'</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F6" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G6" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H6" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="49" t="inlineStr">
+        <is>
+          <t>Jul 2023</t>
+        </is>
+      </c>
+      <c r="J6" s="49" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>https://energyforgrowth.org/article/a-review-of-trinidad-and-tobagos-electricity-sector-and-ppa-process/</t>
+        </is>
+      </c>
+      <c r="L6" s="48" t="inlineStr">
+        <is>
+          <t>Confirms availability / take-or-pay structure (matches your 97% capacity / 3% energy). Embedded equity return is CONFIDENTIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>Damodaran — Country Risk 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>Trinidad &amp; Tobago vs US mature market</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>n/a (add-on)</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>Country risk premium ~4.0% (total ERP 8.35%; US ERP 4.33%)</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I7" s="49" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="J7" s="49" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html</t>
+        </is>
+      </c>
+      <c r="L7" s="48" t="inlineStr">
+        <is>
+          <t>The EM add-on to cost of equity. Ba2 basis. Jamaica 8.9% / Guyana 6.3% for context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>Moody's / S&amp;P — T&amp;T sovereign</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>Offtaker backstop (T&amp;TEC is quasi-sovereign)</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>Ba2 negative (Moody's, Dec-25) / BBB- negative (S&amp;P)</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G8" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H8" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J8" s="49" t="inlineStr">
+        <is>
+          <t>Official/3rd-party</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>https://www.finance.gov.tt/2025/12/12/media-release-moodys-maintains-the-ba2-government-of-trinidad-and-tobago-credit-rating-notwithstanding-short-term-headwinds/</t>
+        </is>
+      </c>
+      <c r="L8" s="48" t="inlineStr">
+        <is>
+          <t>Split rating, negative outlook. Offtaker credit is the key risk to price, NOT volume risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>Derived (build-up) — subject-asset benchmark</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Operating, fully-contracted T&amp;T availability asset</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>Operating, mid-life</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>~11-14% equity IRR; ~8-10% unlevered</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="inlineStr">
+        <is>
+          <t>Post-tax</t>
+        </is>
+      </c>
+      <c r="H9" s="49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I9" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J9" s="49" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>https://energyforgrowth.org/article/a-review-of-trinidad-and-tobagos-electricity-sector-and-ppa-process/</t>
+        </is>
+      </c>
+      <c r="L9" s="48" t="inlineStr">
+        <is>
+          <t>DERIVED (CAPM build-up + TGU debt + generic contracted-IPP hurdle). NOT a disclosed transaction. See Synthesis tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>Trinity Power / PowerGen — PPA expiries</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>Near-end-of-contract T&amp;T comps</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>Near end of PPA</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>Trinity Power PPA expires ~2028; PowerGen 2029 &amp; 2037; TGU ~2041</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H10" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="49" t="inlineStr">
+        <is>
+          <t>2023-26</t>
+        </is>
+      </c>
+      <c r="J10" s="49" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>https://newsday.co.tt/2024/07/20/saying-good-bye-to-powergen/</t>
+        </is>
+      </c>
+      <c r="L10" s="48" t="inlineStr">
+        <is>
+          <t>PowerGen 2014 renewal is the local re-contracting precedent: offtake cut ~20%, Port of Spain plant retired. Draft National Electricity Policy (Jan-26) proposes competitive reform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>UNITED STATES — PJM / ISO-NE capacity markets (merchant new-build ceiling &amp; regulated floor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>Brattle CONE report for PJM</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>New reference gas CT/CC (sets Cost of New Entry)</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>New-build (merchant)</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>ATWACC 9.5%; implied ROE 16.0%; CoD 5.8%; 55/45</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC) &amp; equity</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G12" s="52" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H12" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I12" s="52" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="J12" s="52" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>https://www.pjm.com/-/media/DotCom/committees-groups/committees/mic/2025/20250411-special/item-1-02-revised-cone-report-final.pdf</t>
+        </is>
+      </c>
+      <c r="L12" s="51" t="inlineStr">
+        <is>
+          <t>MERCHANT new-build reference (earns capacity + energy margin). Upper bound, NOT a contracted asset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>Brattle CONE for PJM (2026/27)</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>New reference CT/CC</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>New-build (merchant)</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>ATWACC 8.85%</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC)</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H13" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I13" s="52" t="inlineStr">
+        <is>
+          <t>Apr 2022</t>
+        </is>
+      </c>
+      <c r="J13" s="52" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>https://www.pjm.com/-/media/DotCom/library/reports-notices/special-reports/2022/20220422-brattle-final-cone-report.pdf</t>
+        </is>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>Lower-rate-era vintage; shows the rate rising with base rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>ISO-NE / consultants — CONE &amp; Net CONE</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>New reference CC</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>New-build (merchant)</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="inlineStr">
+        <is>
+          <t>ATWACC 8.3% nom / 6.1% REAL (2020); 8.96% &amp; ROE 13.8% (2023)</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>Unlevered &amp; equity</t>
+        </is>
+      </c>
+      <c r="F14" s="52" t="inlineStr">
+        <is>
+          <t>Both given</t>
+        </is>
+      </c>
+      <c r="G14" s="52" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H14" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I14" s="52" t="inlineStr">
+        <is>
+          <t>2020-23</t>
+        </is>
+      </c>
+      <c r="J14" s="52" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K14" s="31" t="inlineStr">
+        <is>
+          <t>https://www.iso-ne.com/static-assets/documents/2020/08/a4_a_iii_cea_presentation_cone_and_ortp_analysis.pdf</t>
+        </is>
+      </c>
+      <c r="L14" s="51" t="inlineStr">
+        <is>
+          <t>One of the few sources giving BOTH real and nominal (≈2.2% inflation wedge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>Brattle CONE for ERCOT</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>Energy-only merchant reference</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>New-build (merchant)</t>
+        </is>
+      </c>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t>Base ATWACC 10.35% (+100 bps merchant premium debated)</t>
+        </is>
+      </c>
+      <c r="E15" s="52" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC)</t>
+        </is>
+      </c>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G15" s="52" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H15" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I15" s="52" t="inlineStr">
+        <is>
+          <t>Aug 2024</t>
+        </is>
+      </c>
+      <c r="J15" s="52" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>https://www.brattle.com/wp-content/uploads/2024/08/ERCOT-CONE-for-2026.pdf</t>
+        </is>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>MERCHANT, energy-only — upper-bound contrast only. Do not use as a contracted benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>FERC — allowed transmission ROE</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>Regulated cost-of-service (equity floor proxy)</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>Operating (regulated)</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="inlineStr">
+        <is>
+          <t>Base ROE 9.3-9.98%</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H16" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I16" s="52" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J16" s="52" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K16" s="31" t="inlineStr">
+        <is>
+          <t>https://www.ferc.gov/news-events/news/ferc-revises-public-utility-roe-methodology-sets-policy-natural-gas-oil-pipelines</t>
+        </is>
+      </c>
+      <c r="L16" s="51" t="inlineStr">
+        <is>
+          <t>Natural equity floor for a de-risked, contracted cash-flow stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>NRG Energy — LS Power gas acquisition</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>Corporate hurdle for gas-fleet M&amp;A</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>Operating (merchant + capacity)</t>
+        </is>
+      </c>
+      <c r="D17" s="50" t="inlineStr">
+        <is>
+          <t>12-15% unlevered pre-tax; deal at ~7.5x EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="E17" s="52" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G17" s="52" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H17" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I17" s="52" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="J17" s="52" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>https://investors.nrg.com/news-releases/news-release-details/nrg-energy-inc-acquire-premier-power-portfolio-ls-power</t>
+        </is>
+      </c>
+      <c r="L17" s="51" t="inlineStr">
+        <is>
+          <t>Retains merchant/capacity upside — this is the majors-table figure. Contracted-only asset sits below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>Triangulated (US)</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>Operating, fully-contracted capacity asset</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>Operating, mid-life</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="inlineStr">
+        <is>
+          <t>~9-12% levered equity / ~7-9% WACC</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G18" s="52" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H18" s="52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I18" s="52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J18" s="52" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="K18" s="31" t="inlineStr">
+        <is>
+          <t>https://www.pjm.com/-/media/DotCom/committees-groups/committees/mic/2025/20250411-special/item-1-02-revised-cone-report-final.pdf</t>
+        </is>
+      </c>
+      <c r="L18" s="51" t="inlineStr">
+        <is>
+          <t>Between FERC ROE floor (~9.3-10%) and merchant CONE equity ceiling (13-16%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>GREAT BRITAIN &amp; IRELAND — capacity markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>BEIS/DESNZ — Electricity Generation Costs / NERA</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>Unabated gas new-build (CCGT/OCGT) — the net-CONE reference</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>New-build</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="inlineStr">
+        <is>
+          <t>Hurdle rate ~7.8% (CCGT 7.5%)</t>
+        </is>
+      </c>
+      <c r="E20" s="55" t="inlineStr">
+        <is>
+          <t>Unlevered (project)</t>
+        </is>
+      </c>
+      <c r="F20" s="55" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G20" s="55" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H20" s="55" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I20" s="55" t="inlineStr">
+        <is>
+          <t>2016-20</t>
+        </is>
+      </c>
+      <c r="J20" s="55" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/5a8155f2e5274a2e87dbd11b/BEIS_Electricity_Generation_Cost_Report.pdf</t>
+        </is>
+      </c>
+      <c r="L20" s="54" t="inlineStr">
+        <is>
+          <t>~7.8% real ≈ 9.5-10% nominal. Merchant new-build; revenue support LOWERS it. Best 'contracted thermal new-build' proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>DESNZ — Electricity Generation Costs 2025</t>
+        </is>
+      </c>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>Gas + carbon capture (CCUS), DPA-contracted</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>New-build (contracted)</t>
+        </is>
+      </c>
+      <c r="D21" s="53" t="inlineStr">
+        <is>
+          <t>8.9% hurdle (mature)</t>
+        </is>
+      </c>
+      <c r="E21" s="55" t="inlineStr">
+        <is>
+          <t>Unlevered (project)</t>
+        </is>
+      </c>
+      <c r="F21" s="55" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="G21" s="55" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H21" s="55" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I21" s="55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J21" s="55" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69ba657326909a14239612e3/electricity-generation-costs-report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L21" s="54" t="inlineStr">
+        <is>
+          <t>NOTE: 8.9% is CCUS (contracted via DPA), NOT unabated gas. Don't cite as the merchant hurdle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>SEM (Ireland/NI) — Best New Entrant, CEPA/Ramboll</t>
+        </is>
+      </c>
+      <c r="B22" s="54" t="inlineStr">
+        <is>
+          <t>OCGT peaker (I-SEM capacity market)</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>New-build</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>Pre-tax NOMINAL WACC 9.27%; net-CONE €107/kW-yr</t>
+        </is>
+      </c>
+      <c r="E22" s="55" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC)</t>
+        </is>
+      </c>
+      <c r="F22" s="55" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G22" s="55" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H22" s="55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I22" s="55" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J22" s="55" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>https://www.semcommittee.com/publications/sem-23-016-best-new-entrant-decision-paper</t>
+        </is>
+      </c>
+      <c r="L22" s="54" t="inlineStr">
+        <is>
+          <t>Peaker BNE WACC — directly comparable capacity-market hurdle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="53" t="inlineStr">
+        <is>
+          <t>Ofgem — interconnector cap &amp; floor (Nemo Link)</t>
+        </is>
+      </c>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>Availability-based REGULATED analog</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>Operating (regulated)</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>Weighted WACC ~3.9% real; floor=CoD, cap=CoE on 100% RAV</t>
+        </is>
+      </c>
+      <c r="E23" s="55" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC)</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G23" s="55" t="inlineStr">
+        <is>
+          <t>Vanilla</t>
+        </is>
+      </c>
+      <c r="H23" s="55" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I23" s="55" t="inlineStr">
+        <is>
+          <t>2019-24</t>
+        </is>
+      </c>
+      <c r="J23" s="55" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>https://www.ofgem.gov.uk/sites/default/files/2021-09/Regime%20Handbook.pdf</t>
+        </is>
+      </c>
+      <c r="L23" s="54" t="inlineStr">
+        <is>
+          <t>Lowest anchor — a genuinely availability-remunerated, fully de-risked regulated asset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>GB Capacity Market — parameters/auctions</t>
+        </is>
+      </c>
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t>Technology-neutral de-rated capacity</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>All stages</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="inlineStr">
+        <is>
+          <t>Net-CONE ~£49/kW-yr; T-4 clears £6-65/kW-yr</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G24" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="55" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I24" s="55" t="inlineStr">
+        <is>
+          <t>2018-25</t>
+        </is>
+      </c>
+      <c r="J24" s="55" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>https://www.ofgem.gov.uk/sites/default/files/2025-09/annual-report-capacity-market-operations-2024-25.pdf</t>
+        </is>
+      </c>
+      <c r="L24" s="54" t="inlineStr">
+        <is>
+          <t>Capacity PRICE, not a return. Volatile; net-CONE is the admin anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="53" t="inlineStr">
+        <is>
+          <t>Triangulated (GB)</t>
+        </is>
+      </c>
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>Operating, fully-contracted availability asset</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>Operating, mid-life</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>High-single-digit unlevered / low-double-digit levered equity</t>
+        </is>
+      </c>
+      <c r="E25" s="55" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G25" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="55" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I25" s="55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J25" s="55" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/hurdle-rate-estimates-for-electricity-sector-technologies</t>
+        </is>
+      </c>
+      <c r="L25" s="54" t="inlineStr">
+        <is>
+          <t>Below the ~7.8% real (~9.5-10% nom) merchant new-build hurdle; above ~3.9% real regulated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>LATIN AMERICA — statutory capacity / reliability remuneration (mostly REAL, pre-tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>Peru — OSINERGMIN, potencia firme</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="inlineStr">
+        <is>
+          <t>Reference peaker annuity (precio basico de la potencia)</t>
+        </is>
+      </c>
+      <c r="C27" s="58" t="inlineStr">
+        <is>
+          <t>Operating (statutory)</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t>12% real</t>
+        </is>
+      </c>
+      <c r="E27" s="58" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="F27" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G27" s="58" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H27" s="58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="I27" s="58" t="inlineStr">
+        <is>
+          <t>statutory</t>
+        </is>
+      </c>
+      <c r="J27" s="58" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K27" s="59" t="inlineStr">
+        <is>
+          <t>https://www.osinergmin.gob.pe/Resoluciones/pdf/2024/Informe-Tecnico-127-2024-GRT.pdf</t>
+        </is>
+      </c>
+      <c r="L27" s="57" t="inlineStr">
+        <is>
+          <t>Statutory 'tasa de actualizacion' used to annualise the reference peaker's cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>Chile — CNE, pago por potencia</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="inlineStr">
+        <is>
+          <t>Reference gas-turbine annuity</t>
+        </is>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>Operating (statutory)</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>~10% real</t>
+        </is>
+      </c>
+      <c r="E28" s="58" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="F28" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G28" s="58" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H28" s="58" t="inlineStr">
+        <is>
+          <t>CLP/USD</t>
+        </is>
+      </c>
+      <c r="I28" s="58" t="inlineStr">
+        <is>
+          <t>statutory</t>
+        </is>
+      </c>
+      <c r="J28" s="58" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K28" s="59" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/en/tarificacion/electrica/precio-nudo-corto-plazo/</t>
+        </is>
+      </c>
+      <c r="L28" s="57" t="inlineStr">
+        <is>
+          <t>Legacy statutory discount rate for the capacity annuity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>Colombia — CREG methodology (Res. 003/2021)</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="inlineStr">
+        <is>
+          <t>Regulated discount rate (exemplar: transmission)</t>
+        </is>
+      </c>
+      <c r="C29" s="58" t="inlineStr">
+        <is>
+          <t>Operating (regulated)</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t>~10.94% real</t>
+        </is>
+      </c>
+      <c r="E29" s="58" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC)</t>
+        </is>
+      </c>
+      <c r="F29" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G29" s="58" t="inlineStr">
+        <is>
+          <t>Pre-tax</t>
+        </is>
+      </c>
+      <c r="H29" s="58" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="I29" s="58" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J29" s="58" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K29" s="59" t="inlineStr">
+        <is>
+          <t>https://gestornormativo.creg.gov.co/gestor/entorno/docs/pdf/doc_creg_0003_2021.pdf</t>
+        </is>
+      </c>
+      <c r="L29" s="57" t="inlineStr">
+        <is>
+          <t>Cargo por Confiabilidad remuneration is auction-set (US$/MWh); this is the CREG WACC method exemplar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="56" t="inlineStr">
+        <is>
+          <t>Brazil — ANEEL regulatory WACC</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="inlineStr">
+        <is>
+          <t>Regulated generation/transmission tariff assets</t>
+        </is>
+      </c>
+      <c r="C30" s="58" t="inlineStr">
+        <is>
+          <t>Operating (regulated)</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t>~8.0% real after-tax (~12.1% pre-tax)</t>
+        </is>
+      </c>
+      <c r="E30" s="58" t="inlineStr">
+        <is>
+          <t>Unlevered (WACC)</t>
+        </is>
+      </c>
+      <c r="F30" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G30" s="58" t="inlineStr">
+        <is>
+          <t>After-tax</t>
+        </is>
+      </c>
+      <c r="H30" s="58" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I30" s="58" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="J30" s="58" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K30" s="59" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/aneel/pt-br/assuntos/noticias/2026/aneel-atualiza-taxa-regulatoria-de-remuneracao-do-capital-wacc-regulatorio</t>
+        </is>
+      </c>
+      <c r="L30" s="57" t="inlineStr">
+        <is>
+          <t>Regulated rate-base return — a floor for guaranteed cash flows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>Brazil — LRCAP capacity reserve auction (XP analyst model)</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="inlineStr">
+        <is>
+          <t>NEW gas thermal, 15-yr fixed-revenue (receita fixa) availability contract</t>
+        </is>
+      </c>
+      <c r="C31" s="58" t="inlineStr">
+        <is>
+          <t>New-build (contracted)</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>~10% real unlevered viability hurdle</t>
+        </is>
+      </c>
+      <c r="E31" s="58" t="inlineStr">
+        <is>
+          <t>Unlevered</t>
+        </is>
+      </c>
+      <c r="F31" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G31" s="58" t="inlineStr">
+        <is>
+          <t>Pre-financing</t>
+        </is>
+      </c>
+      <c r="H31" s="58" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I31" s="58" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="J31" s="58" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K31" s="59" t="inlineStr">
+        <is>
+          <t>https://researchxp1.s3.sa-east-1.amazonaws.com/2025.11.30+-+ENEV+IoC.pdf</t>
+        </is>
+      </c>
+      <c r="L31" s="57" t="inlineStr">
+        <is>
+          <t>CLOSEST structural analogue: a 15-yr availability capacity contract. ~10% real is the MARGINAL new-build hurdle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="56" t="inlineStr">
+        <is>
+          <t>Brazil — Eneva (listed platform)</t>
+        </is>
+      </c>
+      <c r="B32" s="57" t="inlineStr">
+        <is>
+          <t>De-risked contracted gas platform</t>
+        </is>
+      </c>
+      <c r="C32" s="58" t="inlineStr">
+        <is>
+          <t>Operating/equity</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t>Cost of equity ~10-13% real; &gt;20% real realised (levered, M&amp;A alpha)</t>
+        </is>
+      </c>
+      <c r="E32" s="58" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F32" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G32" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="58" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I32" s="58" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="J32" s="58" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K32" s="59" t="inlineStr">
+        <is>
+          <t>https://researchxp1.s3.sa-east-1.amazonaws.com/2025.11.30+-+ENEV+IoC.pdf</t>
+        </is>
+      </c>
+      <c r="L32" s="57" t="inlineStr">
+        <is>
+          <t>Realised &gt;20% includes development/M&amp;A alpha, NOT a steady-state contracted-asset discount rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="56" t="inlineStr">
+        <is>
+          <t>Brazil — Eneva Corporate Presentation Apr-2026 (slide 13)</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="inlineStr">
+        <is>
+          <t>Eneva's OWN project real IRRs (see 'Eneva Project IRRs' tab)</t>
+        </is>
+      </c>
+      <c r="C33" s="58" t="inlineStr">
+        <is>
+          <t>New-build &amp; operating</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t>Existing ~10-30% leveraged; LRCAP hubs ~14-27% unlevered</t>
+        </is>
+      </c>
+      <c r="E33" s="58" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F33" s="58" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="G33" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="58" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I33" s="58" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="J33" s="58" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K33" s="59" t="inlineStr">
+        <is>
+          <t>https://ri.eneva.com.br/en/financial-information/presentations-and-conference-calls/</t>
+        </is>
+      </c>
+      <c r="L33" s="57" t="inlineStr">
+        <is>
+          <t>Eneva's OWN advantaged returns (captive cheap gas), NOT the market hurdle. Read off a chart (approximate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>Colombia — Cargo por Confiabilidad auction</t>
+        </is>
+      </c>
+      <c r="B34" s="57" t="inlineStr">
+        <is>
+          <t>Firm-energy remuneration (reference OCGT)</t>
+        </is>
+      </c>
+      <c r="C34" s="58" t="inlineStr">
+        <is>
+          <t>New/operating</t>
+        </is>
+      </c>
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t>Auction price ~US$15.1/MWh (2019); ~US$18.2 (2024)</t>
+        </is>
+      </c>
+      <c r="E34" s="58" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F34" s="58" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G34" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I34" s="58" t="inlineStr">
+        <is>
+          <t>2019-24</t>
+        </is>
+      </c>
+      <c r="J34" s="58" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K34" s="59" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine-latam.com/2019/03/01/colombia-asigna-139-gw-de-solar-y-eolica-en-la-subasta-de-cargo-por-confiabilidad/</t>
+        </is>
+      </c>
+      <c r="L34" s="57" t="inlineStr">
+        <is>
+          <t>Capacity PRICE (US$/MWh of firm energy), not a return rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>CROSS-MARKET — availability/contracted infrastructure equity IRRs &amp; spreads</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="60" t="inlineStr">
+        <is>
+          <t>International Public Partnerships (INPP)</t>
+        </is>
+      </c>
+      <c r="B36" s="61" t="inlineStr">
+        <is>
+          <t>98% availability-PPP / regulated portfolio</t>
+        </is>
+      </c>
+      <c r="C36" s="62" t="inlineStr">
+        <is>
+          <t>Operating, contracted</t>
+        </is>
+      </c>
+      <c r="D36" s="60" t="inlineStr">
+        <is>
+          <t>Discount rate 9.0% (risk premium 4.60%)</t>
+        </is>
+      </c>
+      <c r="E36" s="62" t="inlineStr">
+        <is>
+          <t>Equity (fund)</t>
+        </is>
+      </c>
+      <c r="F36" s="62" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G36" s="62" t="inlineStr">
+        <is>
+          <t>Post-tax</t>
+        </is>
+      </c>
+      <c r="H36" s="62" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I36" s="62" t="inlineStr">
+        <is>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="J36" s="62" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K36" s="63" t="inlineStr">
+        <is>
+          <t>https://www.internationalpublicpartnerships.com/media/mnoa1kp4/inpp-2024-annual-report-vf.pdf</t>
+        </is>
+      </c>
+      <c r="L36" s="61" t="inlineStr">
+        <is>
+          <t>Blend incl. regulated; elevated risk premium in high-rate env. Pure availability sleeve prices slightly below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>HICL Infrastructure</t>
+        </is>
+      </c>
+      <c r="B37" s="61" t="inlineStr">
+        <is>
+          <t>~60% availability-PPP portfolio</t>
+        </is>
+      </c>
+      <c r="C37" s="62" t="inlineStr">
+        <is>
+          <t>Operating, contracted</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>Weighted-avg discount rate 8.4%</t>
+        </is>
+      </c>
+      <c r="E37" s="62" t="inlineStr">
+        <is>
+          <t>Equity (fund)</t>
+        </is>
+      </c>
+      <c r="F37" s="62" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G37" s="62" t="inlineStr">
+        <is>
+          <t>Post-tax</t>
+        </is>
+      </c>
+      <c r="H37" s="62" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I37" s="62" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="J37" s="62" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K37" s="63" t="inlineStr">
+        <is>
+          <t>https://www.hicl.com/wp-content/uploads/2025/05/HICL_Interactive-Annual-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L37" s="61" t="inlineStr">
+        <is>
+          <t>Availability-PPP heavy; among the lowest-risk contracted-infra discount rates disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>The Renewables Infrastructure Group (TRIG)</t>
+        </is>
+      </c>
+      <c r="B38" s="61" t="inlineStr">
+        <is>
+          <t>67% fixed-revenue contracted renewables</t>
+        </is>
+      </c>
+      <c r="C38" s="62" t="inlineStr">
+        <is>
+          <t>Operating, mid-life</t>
+        </is>
+      </c>
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>Weighted-avg discount rate 8.6% (FY24)</t>
+        </is>
+      </c>
+      <c r="E38" s="62" t="inlineStr">
+        <is>
+          <t>Equity (fund)</t>
+        </is>
+      </c>
+      <c r="F38" s="62" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G38" s="62" t="inlineStr">
+        <is>
+          <t>Post-tax</t>
+        </is>
+      </c>
+      <c r="H38" s="62" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I38" s="62" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="J38" s="62" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K38" s="63" t="inlineStr">
+        <is>
+          <t>https://www.trig-ltd.com/wp-content/uploads/2025/02/TRIG-FY-2024-Annual-Results-Presentation.pdf</t>
+        </is>
+      </c>
+      <c r="L38" s="61" t="inlineStr">
+        <is>
+          <t>Operating, contracted-heavy — near the developed-market 'floor'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>Greencoat UK Wind</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="inlineStr">
+        <is>
+          <t>Contracted renewables (fixed + merchant tail)</t>
+        </is>
+      </c>
+      <c r="C39" s="62" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>9.0% unlevered / 11% levered; lower rate for contracted vs merchant</t>
+        </is>
+      </c>
+      <c r="E39" s="62" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F39" s="62" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G39" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="62" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I39" s="62" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="J39" s="62" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K39" s="63" t="inlineStr">
+        <is>
+          <t>https://www.greencoat-ukwind.com/</t>
+        </is>
+      </c>
+      <c r="L39" s="61" t="inlineStr">
+        <is>
+          <t>Explicitly discounts contracted cash flows at a LOWER rate than merchant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>Grant Thornton — Renewable Energy Cost of Capital survey</t>
+        </is>
+      </c>
+      <c r="B40" s="61" t="inlineStr">
+        <is>
+          <t>Contracted vs merchant, same asset</t>
+        </is>
+      </c>
+      <c r="C40" s="62" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D40" s="60" t="inlineStr">
+        <is>
+          <t>Merchant carries +100-300 bps over contracted</t>
+        </is>
+      </c>
+      <c r="E40" s="62" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F40" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="62" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="J40" s="62" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K40" s="63" t="inlineStr">
+        <is>
+          <t>https://www.grantthornton.ie/globalassets/1.-member-firms/ireland/insights/publications/grant-thornton---renewable-energy.pdf</t>
+        </is>
+      </c>
+      <c r="L40" s="61" t="inlineStr">
+        <is>
+          <t>Quantifies the contracted DISCOUNT vs merchant: ~1-3 pp lower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>Green Giraffe Advisory</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="inlineStr">
+        <is>
+          <t>Construction vs operating, same asset</t>
+        </is>
+      </c>
+      <c r="C41" s="62" t="inlineStr">
+        <is>
+          <t>New-build vs operating</t>
+        </is>
+      </c>
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>Construction +100-200 bps over operating</t>
+        </is>
+      </c>
+      <c r="E41" s="62" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="F41" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="62" t="inlineStr">
+        <is>
+          <t>recent</t>
+        </is>
+      </c>
+      <c r="J41" s="62" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K41" s="63" t="inlineStr">
+        <is>
+          <t>https://green-giraffe.com/publication/blog-post/the-price-is-right-how-much-is-your-renewable-energy-project-really-worth/</t>
+        </is>
+      </c>
+      <c r="L41" s="61" t="inlineStr">
+        <is>
+          <t>The construction/new-build premium for a contracted asset (low end of the 150-300 bps range).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>Energy-IB valuation convention</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="inlineStr">
+        <is>
+          <t>Investment-grade contracted (long PPA)</t>
+        </is>
+      </c>
+      <c r="C42" s="62" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>6-9% unlevered / 8-12% levered; merchant tail 12-15%</t>
+        </is>
+      </c>
+      <c r="E42" s="62" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F42" s="62" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G42" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="62" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="J42" s="62" t="inlineStr">
+        <is>
+          <t>3rd-party</t>
+        </is>
+      </c>
+      <c r="K42" s="63" t="inlineStr">
+        <is>
+          <t>https://ibinterviewquestions.com/guides/energy-investment-banking/renewable-energy-valuation-methods</t>
+        </is>
+      </c>
+      <c r="L42" s="61" t="inlineStr">
+        <is>
+          <t>Practitioner convention; also gives the +300-600 bps merchant-tail step-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>IFC — Returns on infra equity</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="inlineStr">
+        <is>
+          <t>266 core-infra equity investments, EM vs DM</t>
+        </is>
+      </c>
+      <c r="C43" s="62" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D43" s="60" t="inlineStr">
+        <is>
+          <t>EM excess return ~+2.0 pp/yr over developed markets</t>
+        </is>
+      </c>
+      <c r="E43" s="62" t="inlineStr">
+        <is>
+          <t>Equity (realised)</t>
+        </is>
+      </c>
+      <c r="F43" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J43" s="62" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K43" s="63" t="inlineStr">
+        <is>
+          <t>https://www.ifc.org/en/insights-reports/2025/financial-returns-on-equity-investments-in-infrastructure</t>
+        </is>
+      </c>
+      <c r="L43" s="61" t="inlineStr">
+        <is>
+          <t>Evidence-based EM premium floor (more conservative than Damodaran's ~4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>NAO (UK)</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="inlineStr">
+        <is>
+          <t>Listed availability-PPP infrastructure</t>
+        </is>
+      </c>
+      <c r="C44" s="62" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="D44" s="60" t="inlineStr">
+        <is>
+          <t>Realised investor return 7.3%/yr (2024)</t>
+        </is>
+      </c>
+      <c r="E44" s="62" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F44" s="62" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="G44" s="62" t="inlineStr">
+        <is>
+          <t>Post-tax</t>
+        </is>
+      </c>
+      <c r="H44" s="62" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I44" s="62" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J44" s="62" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="K44" s="63" t="inlineStr">
+        <is>
+          <t>https://www.nao.org.uk/wp-content/uploads/2025/03/lessons-learned-private-finance-for-infrastructure.pdf</t>
+        </is>
+      </c>
+      <c r="L44" s="61" t="inlineStr">
+        <is>
+          <t>Realised (not target) return for availability-PPP; drifts with gilt yields.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId36"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="24" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
+        <is>
+          <t>Capacity-contract IRR benchmark — synthesis &amp; recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Subject asset: OPERATING, fully-contracted power plant in Trinidad &amp; Tobago; ~97% capacity (availability) revenue, ~3% energy. Compiled Jul-2026 from 6 parallel research streams (T&amp;T, US PJM/ISO-NE, GB/Ireland, LatAm, cross-market infra funds, contract-lifecycle). Data &amp; links on the 'Capacity IRR Benchmarks' tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>1) The core point</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>• A ~97%-capacity asset is NOT a merchant generator — it is availability-based. You are paid to be available, not to dispatch, so the discount rate should exclude the dispatch/spread/volume risk premium that merchant hurdles carry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>• So the right benchmark is a CONTRACTED / availability-based return, which sits BETWEEN a regulated utility WACC (floor) and a merchant developer hurdle (ceiling). Grant Thornton quantifies the contracted discount at ~100-300 bps below an otherwise-identical merchant plant; Greencoat and DESNZ (CCUS) confirm the direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>• In Trinidad &amp; Tobago the dominant risks are NOT volume/merchant — they are (a) country risk and (b) T&amp;TEC offtaker credit (loss-making, in arrears, Ba2/BBB- sovereign, negative outlook). Those push the rate back UP, and because the offtaker is quasi-sovereign the country risk is not diversifiable here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>2) The benchmark ladder (what each tier tells you)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>FLOOR — regulated / availability-remunerated returns: Ofgem interconnector cap-floor ~3.9% real (GB); FERC ROE ~9.3-10% nominal (US); ANEEL ~8% real after-tax (Brazil). A pure regulated stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>YOUR ZONE — contracted / availability generation: developed-market ~7-9% levered equity nominal (TRIG 8.6%, HICL 8.4%, INPP 9.0%, Energy-IB 8-12%). LatAm statutory capacity annuities cluster at ~10-12% REAL (Peru 12%, Chile ~10%, Colombia ~11%; Brazil LRCAP new-build viability ~10% real unlevered).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CEILING — merchant new-build hurdle: US CONE ATWACC 8.3-9.5% / ROE 13-16%; GB unabated-gas ~7.8% real (~9.5-10% nominal); NRG 12-15% unlevered. Your asset should be BELOW this on the revenue-risk axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>3) Trinidad &amp; Tobago build-up (the number to use)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Developed-market contracted floor (~7-9% levered equity, nominal USD)  +  T&amp;T country-risk premium (Damodaran ~4.0%; IFC evidence ~+2 pp is a more conservative floor)  +  a T&amp;TEC offtaker-credit spread  −  a small credit for genuinely low volume risk and USD-linked capacity payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Local reality check: TGU's own senior USD debt yields ~8.1% (2025) — so equity must sit meaningfully above that. Generic contracted-IPP equity hurdles run ~12-13%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>RECOMMENDED BENCHMARK — Trinidad &amp; Tobago (nominal, post-tax, USD; levered equity IRR unless noted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Contract-life stage</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>T&amp;T levered equity IRR</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>T&amp;T unlevered / project</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Developed-market equivalent (levered equity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="B21" s="66" t="inlineStr">
+        <is>
+          <t>Operating, fully contracted (mid-life) — YOUR ASSET</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>~11-13%  (central ~12%)</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>~8-10%</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>~7-9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t>New-build, fully contracted</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>~13-15%  (+150-300 bps)</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>~10-12%</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="inlineStr">
+        <is>
+          <t>~9-11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="B23" s="71" t="inlineStr">
+        <is>
+          <t>Near end of PPA / re-contracting</t>
+        </is>
+      </c>
+      <c r="C23" s="72" t="inlineStr">
+        <is>
+          <t>~14-16%+ (renewal-negotiation risk*)</t>
+        </is>
+      </c>
+      <c r="D23" s="73" t="inlineStr">
+        <is>
+          <t>~11-13%+</t>
+        </is>
+      </c>
+      <c r="E23" s="73" t="inlineStr">
+        <is>
+          <t>tail +300-600 bps (12-15% on residual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>Merchant reference (NOT your asset)</t>
+        </is>
+      </c>
+      <c r="C24" s="69" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D24" s="70" t="inlineStr">
+        <is>
+          <t>US CONE 8.3-9.5% WACC / 13-16% ROE; NRG 12-15% unlev</t>
+        </is>
+      </c>
+      <c r="E24" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>* In T&amp;T, end-of-PPA risk is NOT a merchant-price tail (there is no competitive power market) — it is renewal-negotiation / stranded-asset risk with a single distressed monopsony offtaker. Local precedent: PowerGen's 2014 renewal cut offtake ~20% and led to a plant retirement. Trinity Power's PPA expires ~2028; a Draft National Electricity Policy (Jan-2026) proposes competitive-market reform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="65" t="inlineStr">
+        <is>
+          <t>4) How to apply / annotate (per your 'find official reporting then annotate' steer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>• State the basis explicitly. The recommendation above is nominal, post-tax, USD, levered equity. To convert: LatAm statutory rates are REAL (add ~3-5% inflation); GB/US CONE are pre-tax or WACC (not equity); infra-fund rates are nominal post-tax levered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>• Unlevered vs levered: subtract ~150-300 bps from the levered equity figure for an unlevered/project IRR (at typical ~50-60% gearing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>• The single most decisive input is the T&amp;TEC offtaker-credit view. If you can support a stronger (quasi-sovereign, USD-backed) offtaker assumption, the rate moves toward the lower end (~11%); a weaker view pushes it toward/above the upper end (~13-14%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>• Sanity anchors to cite: TGU USD debt ~8.1% (local, hard); Damodaran T&amp;T CRP ~4.0%; Brazil LRCAP ~10% real unlevered (closest structural analogue); developed-market contracted equity 7-9%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="65" t="inlineStr">
+        <is>
+          <t>5) Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>• Basis mismatch is the biggest trap — every headline number above is on a different basis; the columns on the data tab flag it per row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>• No disclosed T&amp;T IPP equity IRR exists (PPAs are confidential). The ~11-14% T&amp;T figure is a reasoned build-up, not an observed transaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>• Verification: this environment's egress policy 403-blocked many official PDFs (PJM, BEIS, CREG, CNE, company IR). Figures were captured via web-search of those official documents; the links are canonical — verify the load-bearing numbers (PJM CONE, BEIS 7.8%, Damodaran T&amp;T, Peru/Chile annuity rates) at source before using in a valuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>• The ~3% energy slice: immaterial, but if it is merchant/volume-exposed it warrants a marginally higher blended rate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/LatAm_Power_Companies_Research.xlsx
+++ b/LatAm_Power_Companies_Research.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Hurdle Rates - Coverage &amp; Gaps" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Capacity IRR Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Capacity IRR - Synthesis" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Capacity IRR - Calculator" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,8 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="14">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,8 +114,36 @@
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00404040"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -167,6 +198,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -240,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -454,6 +495,51 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1070,6 +1156,17 @@
           <t>TRINIDAD &amp; TOBAGO — the direct comps (IPP availability PPAs with T&amp;TEC)</t>
         </is>
       </c>
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+      <c r="J4" s="36" t="n"/>
+      <c r="K4" s="36" t="n"/>
+      <c r="L4" s="37" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="47" t="inlineStr">
@@ -1449,6 +1546,17 @@
           <t>UNITED STATES — PJM / ISO-NE capacity markets (merchant new-build ceiling &amp; regulated floor)</t>
         </is>
       </c>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
+      <c r="L11" s="37" t="n"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="50" t="inlineStr">
@@ -1890,6 +1998,17 @@
           <t>GREAT BRITAIN &amp; IRELAND — capacity markets</t>
         </is>
       </c>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="37" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="53" t="inlineStr">
@@ -2269,6 +2388,17 @@
           <t>LATIN AMERICA — statutory capacity / reliability remuneration (mostly REAL, pre-tax)</t>
         </is>
       </c>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="37" t="n"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="56" t="inlineStr">
@@ -2772,6 +2902,17 @@
           <t>CROSS-MARKET — availability/contracted infrastructure equity IRRs &amp; spreads</t>
         </is>
       </c>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="36" t="n"/>
+      <c r="K35" s="36" t="n"/>
+      <c r="L35" s="37" t="n"/>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="60" t="inlineStr">
@@ -3685,6 +3826,478 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="B1" s="74" t="inlineStr">
+        <is>
+          <t>Capacity-asset discount-rate calculator — Trinidad &amp; Tobago  (CAPM build-up + WACC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="B2" s="75" t="inlineStr">
+        <is>
+          <t>Edit the BLUE cells. The YELLOW cell — T&amp;TEC offtaker credit spread — is the main dial. Black cells are formulas. Three columns = Strong / Base / Weak offtaker-credit views, giving a range. Outputs are nominal USD; real-terms equivalents shown for comparison with LatAm statutory rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Input / Output</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Strong offtaker</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Base case</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Weak offtaker</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Basis / source anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="76" t="inlineStr">
+        <is>
+          <t>INPUTS  (edit the blue / yellow cells)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="77" t="inlineStr">
+        <is>
+          <t>Risk-free rate (US 20Y Treasury, nominal USD)</t>
+        </is>
+      </c>
+      <c r="C6" s="78" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D6" s="78" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E6" s="78" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F6" s="79" t="inlineStr">
+        <is>
+          <t>US Treasury ~4.3% (2026) — update to current</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>Mature-market equity risk premium</t>
+        </is>
+      </c>
+      <c r="C7" s="78" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D7" s="78" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E7" s="78" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="F7" s="79" t="inlineStr">
+        <is>
+          <t>Damodaran US ERP 4.33% (Jan-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="77" t="inlineStr">
+        <is>
+          <t>Asset beta (relevered) — contracted/availability</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="80" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E8" s="80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="79" t="inlineStr">
+        <is>
+          <t>Low: availability revenue ~ no volume risk (~0.4-0.5 unlevered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="77" t="inlineStr">
+        <is>
+          <t>Country risk premium — Trinidad &amp; Tobago</t>
+        </is>
+      </c>
+      <c r="C9" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D9" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E9" s="78" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F9" s="79" t="inlineStr">
+        <is>
+          <t>Damodaran T&amp;T CRP ~4.0% (Ba2); raise for a weaker sovereign view</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="77" t="inlineStr">
+        <is>
+          <t>T&amp;TEC offtaker credit spread  &lt;&lt;&lt; KEY DIAL</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D10" s="81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="81" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F10" s="79" t="inlineStr">
+        <is>
+          <t>The lever: 0.5% = strong quasi-sovereign/USD-backed view; 3.0% = distressed monopsony</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="77" t="inlineStr">
+        <is>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="C11" s="78" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D11" s="78" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E11" s="78" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F11" s="79" t="inlineStr">
+        <is>
+          <t>Anchor: TGU senior USD notes ~8.1% yield (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="77" t="inlineStr">
+        <is>
+          <t>Corporate tax rate (T&amp;T)</t>
+        </is>
+      </c>
+      <c r="C12" s="78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="79" t="inlineStr">
+        <is>
+          <t>T&amp;T corporation tax ~30% — verify for the entity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="77" t="inlineStr">
+        <is>
+          <t>Gearing (debt % of capital)</t>
+        </is>
+      </c>
+      <c r="C13" s="78" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D13" s="78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="79" t="inlineStr">
+        <is>
+          <t>Project finance typical 50-70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="77" t="inlineStr">
+        <is>
+          <t>Expected US inflation (for real conversion)</t>
+        </is>
+      </c>
+      <c r="C14" s="78" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="D14" s="78" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="E14" s="78" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F14" s="79" t="inlineStr">
+        <is>
+          <t>~2.3% — for nominal -&gt; real (Fisher)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="76" t="inlineStr">
+        <is>
+          <t>BUILD-UP  (formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="77" t="inlineStr">
+        <is>
+          <t>Cost of equity  Ke = Rf + β×ERP + CRP + offtaker spread</t>
+        </is>
+      </c>
+      <c r="C16" s="82">
+        <f>C6+C8*C7+C9+C10</f>
+        <v/>
+      </c>
+      <c r="D16" s="82">
+        <f>D6+D8*D7+D9+D10</f>
+        <v/>
+      </c>
+      <c r="E16" s="82">
+        <f>E6+E8*E7+E9+E10</f>
+        <v/>
+      </c>
+      <c r="F16" s="79" t="inlineStr">
+        <is>
+          <t>CAPM build-up with full country risk (offtaker is quasi-sovereign, so CRP applies)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="77" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt = Kd × (1 − tax)</t>
+        </is>
+      </c>
+      <c r="C17" s="82">
+        <f>C11*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="D17" s="82">
+        <f>D11*(1-D12)</f>
+        <v/>
+      </c>
+      <c r="E17" s="82">
+        <f>E11*(1-E12)</f>
+        <v/>
+      </c>
+      <c r="F17" s="79" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="77" t="inlineStr">
+        <is>
+          <t>Equity weight = 1 − gearing</t>
+        </is>
+      </c>
+      <c r="C18" s="82">
+        <f>1-C13</f>
+        <v/>
+      </c>
+      <c r="D18" s="82">
+        <f>1-D13</f>
+        <v/>
+      </c>
+      <c r="E18" s="82">
+        <f>1-E13</f>
+        <v/>
+      </c>
+      <c r="F18" s="79" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="76" t="inlineStr">
+        <is>
+          <t>OUTPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="83" t="inlineStr">
+        <is>
+          <t>&gt;&gt;  Levered equity IRR / discount rate  (nominal, USD)</t>
+        </is>
+      </c>
+      <c r="C20" s="84">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="D20" s="84">
+        <f>D16</f>
+        <v/>
+      </c>
+      <c r="E20" s="84">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="F20" s="85" t="inlineStr">
+        <is>
+          <t>Target LEVERED EQUITY IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>&gt;&gt;  Project / unlevered discount rate — WACC  (nominal, USD)</t>
+        </is>
+      </c>
+      <c r="C21" s="84">
+        <f>C18*C16+C13*C17</f>
+        <v/>
+      </c>
+      <c r="D21" s="84">
+        <f>D18*D16+D13*D17</f>
+        <v/>
+      </c>
+      <c r="E21" s="84">
+        <f>E18*E16+E13*E17</f>
+        <v/>
+      </c>
+      <c r="F21" s="85" t="inlineStr">
+        <is>
+          <t>Unlevered / project discount rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Levered equity IRR  (REAL)</t>
+        </is>
+      </c>
+      <c r="C22" s="82">
+        <f>(1+C20)/(1+C14)-1</f>
+        <v/>
+      </c>
+      <c r="D22" s="82">
+        <f>(1+D20)/(1+D14)-1</f>
+        <v/>
+      </c>
+      <c r="E22" s="82">
+        <f>(1+E20)/(1+E14)-1</f>
+        <v/>
+      </c>
+      <c r="F22" s="79" t="inlineStr">
+        <is>
+          <t>Compare with LatAm statutory REAL rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     WACC  (REAL)</t>
+        </is>
+      </c>
+      <c r="C23" s="82">
+        <f>(1+C21)/(1+C14)-1</f>
+        <v/>
+      </c>
+      <c r="D23" s="82">
+        <f>(1+D21)/(1+D14)-1</f>
+        <v/>
+      </c>
+      <c r="E23" s="82">
+        <f>(1+E21)/(1+E14)-1</f>
+        <v/>
+      </c>
+      <c r="F23" s="79" t="inlineStr">
+        <is>
+          <t>Peru 12% / Chile ~10% / Brazil LRCAP ~10% real</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="B25" s="88" t="inlineStr">
+        <is>
+          <t>Illustrative outputs at the default inputs (the cells above auto-recalculate on open/edit):  Levered equity IRR (Ke) ≈ 11.4% / 12.1% / 15.0%   ·   WACC ≈ 7.4% / 8.2% / 10.7%   ·   Ke real ≈ 8.9% / 9.6% / 12.5%   (Strong / Base / Weak offtaker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="86" t="inlineStr">
+        <is>
+          <t>Benchmark cross-check (operating, fully-contracted T&amp;T): levered equity IRR ~11-13% nominal (central ~12%); unlevered/WACC ~8-10%. Base-case defaults above are set to land in that zone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="86" t="inlineStr">
+        <is>
+          <t>Lifecycle adjustment (apply on top of the output): NEW-BUILD +150-300 bps (construction); NEAR END OF PPA add a renewal-negotiation premium (T&amp;T has no merchant tail — it's re-contracting/stranded-asset risk with a single offtaker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="87" t="inlineStr">
+        <is>
+          <t>Legend:  BLUE = input (edit)   ·   YELLOW = key dial (offtaker spread)   ·   BLACK = formula   ·   GREEN = output.   This is a screening tool, not a substitute for a full project-finance model (debt sculpting, DSCR, tax shields, timing). All figures nominal USD unless labelled REAL.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/LatAm_Power_Companies_Research.xlsx
+++ b/LatAm_Power_Companies_Research.xlsx
@@ -2403,12 +2403,12 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="56" t="inlineStr">
         <is>
-          <t>Peru — OSINERGMIN, potencia firme</t>
+          <t>Peru — LCE (DL 25844) Art. 79 / OSINERGMIN</t>
         </is>
       </c>
       <c r="B27" s="57" t="inlineStr">
         <is>
-          <t>Reference peaker annuity (precio basico de la potencia)</t>
+          <t>Discount rate for regulated tariffs incl. precio basico de la potencia</t>
         </is>
       </c>
       <c r="C27" s="58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H27" s="58" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>constant</t>
         </is>
       </c>
       <c r="I27" s="58" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="K27" s="59" t="inlineStr">
         <is>
-          <t>https://www.osinergmin.gob.pe/Resoluciones/pdf/2024/Informe-Tecnico-127-2024-GRT.pdf</t>
+          <t>https://www.osinergmin.gob.pe/cartas/documentos/electricidad/normativa/LEY_CONCESIONES_ELECTRICAS.pdf</t>
         </is>
       </c>
       <c r="L27" s="57" t="inlineStr">
         <is>
-          <t>Statutory 'tasa de actualizacion' used to annualise the reference peaker's cost.</t>
+          <t>VERIFIED: LCE Art. 79 fixes a 12% real annual 'tasa de actualizacion', used to annualise the reference unit's VNR into the capacity price. It is in the LAW, not a company report.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="56" t="inlineStr">
         <is>
-          <t>Chile — CNE, pago por potencia</t>
+          <t>Chile — CNE (DFL; Leyes 20.936 &amp; 21.194)</t>
         </is>
       </c>
       <c r="B28" s="57" t="inlineStr">
         <is>
-          <t>Reference gas-turbine annuity</t>
+          <t>Regulated cost of capital / capacity-annuity discount rate</t>
         </is>
       </c>
       <c r="C28" s="58" t="inlineStr">
@@ -2480,32 +2480,32 @@
       </c>
       <c r="D28" s="56" t="inlineStr">
         <is>
-          <t>~10% real</t>
+          <t>Legacy 10% real; NOW 7-10% after-tax (transmission), 6-8% (distribution)</t>
         </is>
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Unlevered</t>
+          <t>Unlevered (WACC)</t>
         </is>
       </c>
       <c r="F28" s="58" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G28" s="58" t="inlineStr">
         <is>
-          <t>Pre-tax</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="H28" s="58" t="inlineStr">
         <is>
-          <t>CLP/USD</t>
+          <t>real/AT</t>
         </is>
       </c>
       <c r="I28" s="58" t="inlineStr">
         <is>
-          <t>statutory</t>
+          <t>2016-19</t>
         </is>
       </c>
       <c r="J28" s="58" t="inlineStr">
@@ -2520,19 +2520,19 @@
       </c>
       <c r="L28" s="57" t="inlineStr">
         <is>
-          <t>Legacy statutory discount rate for the capacity annuity.</t>
+          <t>CORRECTED: the fixed 10% real was REFORMED. Law 20.936 (2016) set transmission WACC 7-10% after-tax; Law 21.194 (2019) set distribution 6-8% after-tax. Treat 10% as a legacy upper bound, NOT the current rate.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="56" t="inlineStr">
         <is>
-          <t>Colombia — CREG methodology (Res. 003/2021)</t>
+          <t>Colombia — CREG Res. 103/2021 (natural GAS TRANSPORT)</t>
         </is>
       </c>
       <c r="B29" s="57" t="inlineStr">
         <is>
-          <t>Regulated discount rate (exemplar: transmission)</t>
+          <t>Regulated WACC for gas transport (TGI / Promigas)</t>
         </is>
       </c>
       <c r="C29" s="58" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D29" s="56" t="inlineStr">
         <is>
-          <t>~10.94% real</t>
+          <t>10.94% real (raised to 11.88% in 2023)</t>
         </is>
       </c>
       <c r="E29" s="58" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H29" s="58" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>constant COP</t>
         </is>
       </c>
       <c r="I29" s="58" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="K29" s="59" t="inlineStr">
         <is>
-          <t>https://gestornormativo.creg.gov.co/gestor/entorno/docs/pdf/doc_creg_0003_2021.pdf</t>
+          <t>https://gestornormativo.creg.gov.co/gestor/entorno/docs/resolucion_creg_0103_2021.htm</t>
         </is>
       </c>
       <c r="L29" s="57" t="inlineStr">
         <is>
-          <t>Cargo por Confiabilidad remuneration is auction-set (US$/MWh); this is the CREG WACC method exemplar.</t>
+          <t>CORRECTED: this is the GAS-TRANSPORT discount rate (NOT electricity transmission), raised to 11.88% by Res. 102 002/2023 (same figure as the GEB gas-transport row). The electricity Cargo por Confiabilidad is auction-priced (US$/MWh), NOT a stated WACC.</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
     <row r="12" ht="44" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>YOUR ZONE — contracted / availability generation: developed-market ~7-9% levered equity nominal (TRIG 8.6%, HICL 8.4%, INPP 9.0%, Energy-IB 8-12%). LatAm statutory capacity annuities cluster at ~10-12% REAL (Peru 12%, Chile ~10%, Colombia ~11%; Brazil LRCAP new-build viability ~10% real unlevered).</t>
+          <t>YOUR ZONE — contracted / availability generation: developed-market ~7-9% levered equity nominal (TRIG 8.6%, HICL 8.4%, INPP 9.0%, Energy-IB 8-12%). LatAm regulated/statutory REAL rates: Peru 12% real (LCE Art. 79, verified); Chile legacy 10% real, now 7-10% after-tax post-reform (Laws 20.936/21.194); Colombia gas-transport WACC 10.94-11.88% real (CREG); Brazil ANEEL ~8% real after-tax; Brazil LRCAP new-build viability ~10% real unlevered (XP).</t>
         </is>
       </c>
     </row>
